--- a/reports/2026-10-11/decision-book.xlsx
+++ b/reports/2026-10-11/decision-book.xlsx
@@ -13,7 +13,8 @@
     <sheet name="Decisions" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="SG Income" sheetId="4" state="visible" r:id="rId6"/>
     <sheet name="FX" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Decision Log" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Options" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Decision Log" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Decisions!$A$1:$S$84</definedName>
@@ -49,7 +50,7 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Unknown Author</author>
@@ -72,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="769" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="406">
   <si>
     <t xml:space="preserve">Global Investment Decision Book</t>
   </si>
@@ -170,6 +171,18 @@
     <t xml:space="preserve">Singapore income target: upper bound</t>
   </si>
   <si>
+    <t xml:space="preserve">Options sleeve cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total option premium at risk, share of portfolio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Options per-trade risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premium at risk per option trade</t>
+  </si>
+  <si>
     <t xml:space="preserve">Portfolio tilts this week</t>
   </si>
   <si>
@@ -1110,6 +1123,135 @@
   </si>
   <si>
     <t xml:space="preserve">USD strengthening vs CHF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Underlying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Legs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expiry</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debit / share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cost per contract</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Breakeven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Move to breakeven</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Max gain / share</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reward : risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prob. of profit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contracts (per-trade budget)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Premium at risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stop: close at value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bull call spread</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy 170C / Sell 185C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-12-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bear put spread</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy 385P / Sell 345P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy 350C / Sell 385C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy 335C / Sell 370C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy 140P / Sell 125P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy 230C / Sell 250C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy 751C / Sell 825C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy 779C / Sell 855C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long put</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy 135P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Long call</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy 175C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy 240C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy 370C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy 365P</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy 355C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy 789C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Buy 817C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sleeve check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total if all taken</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sleeve cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Within cap?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Probability of profit is risk-neutral, from the option's implied volatility. Debits are mid prices from IBKR weekend quotes; re-price live before trading. Defined risk only: maximum loss = premium paid.</t>
   </si>
   <si>
     <t xml:space="preserve">Date</t>
@@ -1155,7 +1297,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="10">
+  <numFmts count="12">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0"/>
     <numFmt numFmtId="166" formatCode="0%"/>
@@ -1166,6 +1308,8 @@
     <numFmt numFmtId="171" formatCode="0.000"/>
     <numFmt numFmtId="172" formatCode="0.0000"/>
     <numFmt numFmtId="173" formatCode="0.00%"/>
+    <numFmt numFmtId="174" formatCode="0.0\x"/>
+    <numFmt numFmtId="175" formatCode="General"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -1340,7 +1484,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1459,6 +1603,34 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="174" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="175" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -1869,7 +2041,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C18"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1976,24 +2148,30 @@
         <v>31</v>
       </c>
     </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="8" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="9" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="A11" s="4" t="s">
         <v>34</v>
       </c>
+      <c r="B11" s="8" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="2" t="s">
+      <c r="A13" s="9" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2035,6 +2213,22 @@
       </c>
       <c r="C18" s="2" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -2075,84 +2269,84 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H2" s="13" t="n">
         <v>65.08</v>
@@ -2195,25 +2389,25 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D3" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" s="10" t="s">
+      <c r="E3" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="E3" s="10" t="s">
+      <c r="G3" s="12" t="s">
         <v>76</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>72</v>
       </c>
       <c r="H3" s="13" t="n">
         <v>37.954</v>
@@ -2256,25 +2450,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="C4" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E4" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="12" t="s">
         <v>76</v>
-      </c>
-      <c r="F4" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>72</v>
       </c>
       <c r="H4" s="13" t="n">
         <v>168.94</v>
@@ -2317,25 +2511,25 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H5" s="13" t="n">
         <v>40.31</v>
@@ -2378,25 +2572,25 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H6" s="13" t="n">
         <v>198.78</v>
@@ -2439,25 +2633,25 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H7" s="13" t="n">
         <v>778.57</v>
@@ -2500,25 +2694,25 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E8" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" s="12" t="s">
         <v>76</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>72</v>
       </c>
       <c r="H8" s="13" t="n">
         <v>336.64</v>
@@ -2561,25 +2755,25 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H9" s="13" t="n">
         <v>751.27</v>
@@ -2622,25 +2816,25 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="H10" s="13" t="n">
         <v>170.81</v>
@@ -2683,25 +2877,25 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E11" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G11" s="12" t="s">
         <v>76</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="12" t="s">
-        <v>72</v>
       </c>
       <c r="H11" s="13" t="n">
         <v>351.66</v>
@@ -2744,25 +2938,25 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E12" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="12" t="s">
         <v>76</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>72</v>
       </c>
       <c r="H12" s="13" t="n">
         <v>229.28</v>
@@ -2805,25 +2999,25 @@
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F13" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="H13" s="13" t="n">
         <v>275.04</v>
@@ -2866,25 +3060,25 @@
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D14" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" s="19" t="s">
         <v>111</v>
       </c>
-      <c r="E14" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>107</v>
-      </c>
       <c r="G14" s="12" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="H14" s="13" t="n">
         <v>148.2</v>
@@ -2927,25 +3121,25 @@
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="10" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="H15" s="13" t="n">
         <v>559.4</v>
@@ -2988,25 +3182,25 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H16" s="13" t="n">
         <v>418.78</v>
@@ -3049,25 +3243,25 @@
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H17" s="13" t="n">
         <v>535.07</v>
@@ -3110,25 +3304,25 @@
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="10" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G18" s="12" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="H18" s="13" t="n">
         <v>216.74</v>
@@ -3171,25 +3365,25 @@
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="10" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C19" s="10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H19" s="13" t="n">
         <v>41.42</v>
@@ -3232,25 +3426,25 @@
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="10" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H20" s="13" t="n">
         <v>262.43</v>
@@ -3293,25 +3487,25 @@
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="10" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="B21" s="10" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G21" s="12" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H21" s="13" t="n">
         <v>112.67</v>
@@ -3354,25 +3548,25 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="10" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B22" s="10" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C22" s="10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G22" s="12" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H22" s="13" t="n">
         <v>28.99</v>
@@ -3415,25 +3609,25 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="10" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B23" s="10" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H23" s="13" t="n">
         <v>718.67</v>
@@ -3476,25 +3670,25 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="10" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B24" s="10" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="H24" s="13" t="n">
         <v>140.86</v>
@@ -3537,25 +3731,25 @@
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="10" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B25" s="10" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H25" s="13" t="n">
         <v>27.22</v>
@@ -3598,25 +3792,25 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B26" s="10" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="G26" s="12" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H26" s="13" t="n">
         <v>46.77</v>
@@ -3659,25 +3853,25 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="10" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B27" s="10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C27" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F27" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G27" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H27" s="13" t="n">
         <v>29</v>
@@ -3716,25 +3910,25 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="10" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B28" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="C28" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>152</v>
-      </c>
       <c r="D28" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F28" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G28" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H28" s="13" t="n">
         <v>73.36</v>
@@ -3773,25 +3967,25 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D29" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E29" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F29" s="20" t="s">
         <v>157</v>
       </c>
-      <c r="B29" s="10" t="s">
+      <c r="G29" s="12" t="s">
         <v>158</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="D29" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E29" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="F29" s="20" t="s">
-        <v>153</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>154</v>
       </c>
       <c r="H29" s="13" t="n">
         <v>5.497</v>
@@ -3830,25 +4024,25 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="10" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B30" s="10" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F30" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G30" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H30" s="13" t="n">
         <v>71.16</v>
@@ -3887,25 +4081,25 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="10" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F31" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H31" s="13" t="n">
         <v>13.958</v>
@@ -3944,25 +4138,25 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="10" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B32" s="10" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C32" s="10" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F32" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G32" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H32" s="13" t="n">
         <v>9.83</v>
@@ -4001,25 +4195,25 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="10" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="B33" s="10" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F33" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G33" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H33" s="13" t="n">
         <v>145.2</v>
@@ -4058,25 +4252,25 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="10" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B34" s="10" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F34" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G34" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H34" s="13" t="n">
         <v>24.53</v>
@@ -4115,25 +4309,25 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="10" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="B35" s="10" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C35" s="10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G35" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H35" s="13" t="n">
         <v>82.46</v>
@@ -4172,25 +4366,25 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="10" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G36" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H36" s="13" t="n">
         <v>28.33</v>
@@ -4229,25 +4423,25 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="10" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G37" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H37" s="13" t="n">
         <v>10.266</v>
@@ -4286,25 +4480,25 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="10" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F38" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G38" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H38" s="13" t="n">
         <v>10.42</v>
@@ -4343,25 +4537,25 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="10" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F39" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G39" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H39" s="13" t="n">
         <v>49.43</v>
@@ -4400,25 +4594,25 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="10" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F40" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H40" s="13" t="n">
         <v>13.844</v>
@@ -4457,25 +4651,25 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="10" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F41" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G41" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H41" s="13" t="n">
         <v>1.016</v>
@@ -4514,25 +4708,25 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="10" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F42" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G42" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H42" s="13" t="n">
         <v>332.99</v>
@@ -4571,25 +4765,25 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="10" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="B43" s="10" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F43" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H43" s="13" t="n">
         <v>169.25</v>
@@ -4628,25 +4822,25 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="10" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="B44" s="10" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F44" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G44" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H44" s="13" t="n">
         <v>54.73</v>
@@ -4685,25 +4879,25 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="10" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B45" s="10" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C45" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F45" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H45" s="13" t="n">
         <v>39.96</v>
@@ -4742,25 +4936,25 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="10" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B46" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F46" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G46" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H46" s="13" t="n">
         <v>361.54</v>
@@ -4799,25 +4993,25 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="10" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B47" s="10" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F47" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H47" s="13" t="n">
         <v>4.303</v>
@@ -4856,25 +5050,25 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="10" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B48" s="10" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F48" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G48" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H48" s="13" t="n">
         <v>11.01</v>
@@ -4913,25 +5107,25 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B49" s="10" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F49" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H49" s="13" t="n">
         <v>86.84</v>
@@ -4970,25 +5164,25 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="10" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F50" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G50" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H50" s="13" t="n">
         <v>18.574</v>
@@ -5027,25 +5221,25 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="B51" s="10" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F51" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H51" s="13" t="n">
         <v>41.61</v>
@@ -5084,25 +5278,25 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="C52" s="10" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="E52" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F52" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G52" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H52" s="13" t="n">
         <v>37.32</v>
@@ -5141,25 +5335,25 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B53" s="10" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F53" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H53" s="13" t="n">
         <v>120.24</v>
@@ -5198,25 +5392,25 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B54" s="10" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C54" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="E54" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F54" s="20" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G54" s="12" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H54" s="13" t="n">
         <v>3.98</v>
@@ -5255,25 +5449,25 @@
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F55" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G55" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H55" s="13" t="n">
         <v>83.43</v>
@@ -5312,25 +5506,25 @@
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D56" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="E56" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F56" s="21" t="s">
         <v>225</v>
       </c>
-      <c r="E56" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="F56" s="21" t="s">
-        <v>221</v>
-      </c>
       <c r="G56" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H56" s="13" t="n">
         <v>54.78</v>
@@ -5369,25 +5563,25 @@
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="B57" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="C57" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D57" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="E57" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F57" s="21" t="s">
+        <v>225</v>
+      </c>
+      <c r="G57" s="12" t="s">
         <v>226</v>
-      </c>
-      <c r="B57" s="10" t="s">
-        <v>227</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>81</v>
-      </c>
-      <c r="D57" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="E57" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="F57" s="21" t="s">
-        <v>221</v>
-      </c>
-      <c r="G57" s="12" t="s">
-        <v>222</v>
       </c>
       <c r="H57" s="13" t="n">
         <v>384.58</v>
@@ -5426,25 +5620,25 @@
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B58" s="10" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="C58" s="10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F58" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H58" s="13" t="n">
         <v>52.83</v>
@@ -5483,25 +5677,25 @@
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="B59" s="10" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="E59" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F59" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H59" s="13" t="n">
         <v>17.544</v>
@@ -5540,25 +5734,25 @@
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="10" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B60" s="10" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F60" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H60" s="13" t="n">
         <v>11.48</v>
@@ -5597,25 +5791,25 @@
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="B61" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D61" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="B61" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="C61" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="D61" s="10" t="s">
-        <v>231</v>
-      </c>
       <c r="E61" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F61" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H61" s="13" t="n">
         <v>71.26</v>
@@ -5654,25 +5848,25 @@
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F62" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G62" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H62" s="13" t="n">
         <v>4.24</v>
@@ -5711,25 +5905,25 @@
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="10" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B63" s="10" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F63" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G63" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H63" s="13" t="n">
         <v>110.38</v>
@@ -5768,25 +5962,25 @@
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F64" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G64" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H64" s="13" t="n">
         <v>0.955</v>
@@ -5825,25 +6019,25 @@
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="10" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B65" s="10" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C65" s="10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F65" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H65" s="13" t="n">
         <v>1263</v>
@@ -5882,25 +6076,25 @@
     </row>
     <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="10" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B66" s="10" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C66" s="10" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F66" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G66" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H66" s="13" t="n">
         <v>80.1</v>
@@ -5939,25 +6133,25 @@
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="10" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B67" s="10" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F67" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G67" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H67" s="13" t="n">
         <v>112.85</v>
@@ -5996,25 +6190,25 @@
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="10" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="B68" s="10" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="C68" s="10" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F68" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H68" s="13" t="n">
         <v>24.84</v>
@@ -6053,25 +6247,25 @@
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="10" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="B69" s="10" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="C69" s="10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F69" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G69" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H69" s="13" t="n">
         <v>52.24</v>
@@ -6110,25 +6304,25 @@
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="10" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B70" s="10" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F70" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H70" s="13" t="n">
         <v>141.4</v>
@@ -6167,25 +6361,25 @@
     </row>
     <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="10" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B71" s="10" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C71" s="10" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F71" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G71" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H71" s="13" t="n">
         <v>107</v>
@@ -6224,25 +6418,25 @@
     </row>
     <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="10" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="B72" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="C72" s="10" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F72" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G72" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H72" s="13" t="n">
         <v>377.8</v>
@@ -6281,25 +6475,25 @@
     </row>
     <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="10" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="B73" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="D73" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="C73" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="D73" s="10" t="s">
-        <v>261</v>
-      </c>
       <c r="E73" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F73" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G73" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H73" s="13" t="n">
         <v>71.5</v>
@@ -6338,25 +6532,25 @@
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="10" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B74" s="10" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C74" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F74" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G74" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H74" s="13" t="n">
         <v>2.24</v>
@@ -6395,25 +6589,25 @@
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="10" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B75" s="10" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="F75" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G75" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H75" s="13" t="n">
         <v>41.41</v>
@@ -6452,25 +6646,25 @@
     </row>
     <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="10" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="B76" s="10" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="C76" s="10" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F76" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G76" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H76" s="13" t="n">
         <v>297.75</v>
@@ -6509,25 +6703,25 @@
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="10" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B77" s="10" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="C77" s="10" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F77" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G77" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H77" s="13" t="n">
         <v>75.6</v>
@@ -6566,25 +6760,25 @@
     </row>
     <row r="78" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="10" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B78" s="10" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C78" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F78" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G78" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H78" s="13" t="n">
         <v>2.13</v>
@@ -6623,25 +6817,25 @@
     </row>
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="10" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B79" s="10" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C79" s="10" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F79" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H79" s="13" t="n">
         <v>424.8</v>
@@ -6680,25 +6874,25 @@
     </row>
     <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="10" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B80" s="10" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C80" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F80" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G80" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H80" s="13" t="n">
         <v>1.08</v>
@@ -6737,25 +6931,25 @@
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="10" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B81" s="10" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C81" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F81" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G81" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H81" s="13" t="n">
         <v>1.83</v>
@@ -6794,25 +6988,25 @@
     </row>
     <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="10" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B82" s="10" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C82" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F82" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G82" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H82" s="13" t="n">
         <v>2.07</v>
@@ -6851,25 +7045,25 @@
     </row>
     <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="10" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B83" s="10" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C83" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F83" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G83" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H83" s="13" t="n">
         <v>1.19</v>
@@ -6908,25 +7102,25 @@
     </row>
     <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="10" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B84" s="10" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C84" s="10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F84" s="21" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="G84" s="12" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="H84" s="13" t="n">
         <v>2.19</v>
@@ -6965,10 +7159,10 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="9" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="N86" s="9" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="O86" s="22" t="n">
         <f aca="false">SUM(O2:O84)</f>
@@ -6981,7 +7175,7 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -7020,51 +7214,51 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="C2" s="24" t="n">
         <v>1.83</v>
@@ -7100,18 +7294,18 @@
         <v>-0.144859813084112</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M2" s="29" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C3" s="24" t="n">
         <v>2.19</v>
@@ -7147,18 +7341,18 @@
         <v>-0.22887323943662</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M3" s="29" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C4" s="24" t="n">
         <v>1.08</v>
@@ -7194,18 +7388,18 @@
         <v>-0.142857142857143</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M4" s="29" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="C5" s="24" t="n">
         <v>1.19</v>
@@ -7241,18 +7435,18 @@
         <v>-0.179310344827586</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M5" s="29" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C6" s="24" t="n">
         <v>2.13</v>
@@ -7288,18 +7482,18 @@
         <v>-0.108786610878661</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="M6" s="29" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C7" s="24" t="n">
         <v>2.07</v>
@@ -7335,18 +7529,18 @@
         <v>-0.130252100840336</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M7" s="29" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>0.955</v>
@@ -7382,18 +7576,18 @@
         <v>-0.00520833333333337</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M8" s="29" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="C9" s="24" t="n">
         <v>2.24</v>
@@ -7429,18 +7623,18 @@
         <v>-0.0427350427350426</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M9" s="29" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="C10" s="24" t="n">
         <v>4.24</v>
@@ -7476,18 +7670,18 @@
         <v>-0.00469483568075102</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="M10" s="29" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="4" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C11" s="24" t="n">
         <v>73.36</v>
@@ -7523,18 +7717,18 @@
         <v>0.36230269266481</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M11" s="29" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C12" s="24" t="n">
         <v>3.98</v>
@@ -7570,18 +7764,18 @@
         <v>-0.038647342995169</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M12" s="29" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="C13" s="24" t="n">
         <v>39.96</v>
@@ -7617,18 +7811,18 @@
         <v>0.13105009906595</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M13" s="29" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C14" s="24" t="n">
         <v>29</v>
@@ -7664,18 +7858,18 @@
         <v>0.718009478672986</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M14" s="29" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C15" s="24" t="n">
         <v>10.42</v>
@@ -7711,15 +7905,15 @@
         <v>0.218713450292398</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="M15" s="29" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -7749,27 +7943,27 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D2" s="28" t="n">
         <v>-0.0127528665983034</v>
@@ -7777,13 +7971,13 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="D3" s="28" t="n">
         <v>-0.0188782549659446</v>
@@ -7791,13 +7985,13 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="D4" s="28" t="n">
         <v>-0.00660327522451132</v>
@@ -7805,13 +7999,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D5" s="28" t="n">
         <v>-0.0208884147378512</v>
@@ -7819,13 +8013,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D6" s="28" t="n">
         <v>-0.00849671937600405</v>
@@ -7833,13 +8027,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D7" s="28" t="n">
         <v>0.00107789548878423</v>
@@ -7847,13 +8041,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="D8" s="28" t="n">
         <v>-0.0131264168678695</v>
@@ -7861,13 +8055,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="D9" s="28" t="n">
         <v>0.00377317809400601</v>
@@ -7875,13 +8069,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D10" s="28" t="n">
         <v>0.0268097343764495</v>
@@ -7899,6 +8093,1058 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:Q23"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="13"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>351</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>354</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>356</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>357</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>360</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>363</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>368</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E2" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F2" s="31" t="n">
+        <v>168.79</v>
+      </c>
+      <c r="G2" s="32" t="n">
+        <v>4.87</v>
+      </c>
+      <c r="H2" s="23" t="n">
+        <f aca="false">G2*100</f>
+        <v>487</v>
+      </c>
+      <c r="I2" s="31" t="n">
+        <v>174.87</v>
+      </c>
+      <c r="J2" s="33" t="n">
+        <f aca="false">I2/F2-1</f>
+        <v>0.0360210912968779</v>
+      </c>
+      <c r="K2" s="32" t="n">
+        <v>10.13</v>
+      </c>
+      <c r="L2" s="34" t="n">
+        <f aca="false">IF(K2="","open",K2/G2)</f>
+        <v>2.08008213552361</v>
+      </c>
+      <c r="M2" s="7" t="n">
+        <v>0.387158488416082</v>
+      </c>
+      <c r="N2" s="7" t="n">
+        <v>0.281044545535459</v>
+      </c>
+      <c r="O2" s="35" t="n">
+        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H2)</f>
+        <v>20</v>
+      </c>
+      <c r="P2" s="23" t="n">
+        <f aca="false">O2*H2</f>
+        <v>9740</v>
+      </c>
+      <c r="Q2" s="36" t="n">
+        <f aca="false">G2*(1-0.5)</f>
+        <v>2.435</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E3" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F3" s="31" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="G3" s="32" t="n">
+        <v>10.935</v>
+      </c>
+      <c r="H3" s="23" t="n">
+        <f aca="false">G3*100</f>
+        <v>1093.5</v>
+      </c>
+      <c r="I3" s="31" t="n">
+        <v>374.065</v>
+      </c>
+      <c r="J3" s="33" t="n">
+        <f aca="false">I3/F3-1</f>
+        <v>-0.0271391417425227</v>
+      </c>
+      <c r="K3" s="32" t="n">
+        <v>29.065</v>
+      </c>
+      <c r="L3" s="34" t="n">
+        <f aca="false">IF(K3="","open",K3/G3)</f>
+        <v>2.65797896662094</v>
+      </c>
+      <c r="M3" s="7" t="n">
+        <v>0.369628364966556</v>
+      </c>
+      <c r="N3" s="7" t="n">
+        <v>0.211865064588511</v>
+      </c>
+      <c r="O3" s="35" t="n">
+        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H3)</f>
+        <v>9</v>
+      </c>
+      <c r="P3" s="23" t="n">
+        <f aca="false">O3*H3</f>
+        <v>9841.5</v>
+      </c>
+      <c r="Q3" s="36" t="n">
+        <f aca="false">G3*(1-0.5)</f>
+        <v>5.4675</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E4" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F4" s="31" t="n">
+        <v>351.6</v>
+      </c>
+      <c r="G4" s="32" t="n">
+        <v>13.15</v>
+      </c>
+      <c r="H4" s="23" t="n">
+        <f aca="false">G4*100</f>
+        <v>1315</v>
+      </c>
+      <c r="I4" s="31" t="n">
+        <v>363.15</v>
+      </c>
+      <c r="J4" s="33" t="n">
+        <f aca="false">I4/F4-1</f>
+        <v>0.0328498293515358</v>
+      </c>
+      <c r="K4" s="32" t="n">
+        <v>21.85</v>
+      </c>
+      <c r="L4" s="34" t="n">
+        <f aca="false">IF(K4="","open",K4/G4)</f>
+        <v>1.66159695817491</v>
+      </c>
+      <c r="M4" s="7" t="n">
+        <v>0.403716166404712</v>
+      </c>
+      <c r="N4" s="7" t="n">
+        <v>0.326997925546259</v>
+      </c>
+      <c r="O4" s="35" t="n">
+        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H4)</f>
+        <v>7</v>
+      </c>
+      <c r="P4" s="23" t="n">
+        <f aca="false">O4*H4</f>
+        <v>9205</v>
+      </c>
+      <c r="Q4" s="36" t="n">
+        <f aca="false">G4*(1-0.5)</f>
+        <v>6.575</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>373</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E5" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F5" s="31" t="n">
+        <v>336.08</v>
+      </c>
+      <c r="G5" s="32" t="n">
+        <v>12.65</v>
+      </c>
+      <c r="H5" s="23" t="n">
+        <f aca="false">G5*100</f>
+        <v>1265</v>
+      </c>
+      <c r="I5" s="31" t="n">
+        <v>347.65</v>
+      </c>
+      <c r="J5" s="33" t="n">
+        <f aca="false">I5/F5-1</f>
+        <v>0.0344263270649845</v>
+      </c>
+      <c r="K5" s="32" t="n">
+        <v>22.35</v>
+      </c>
+      <c r="L5" s="34" t="n">
+        <f aca="false">IF(K5="","open",K5/G5)</f>
+        <v>1.76679841897233</v>
+      </c>
+      <c r="M5" s="7" t="n">
+        <v>0.38331306816479</v>
+      </c>
+      <c r="N5" s="7" t="n">
+        <v>0.246064122871679</v>
+      </c>
+      <c r="O5" s="35" t="n">
+        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H5)</f>
+        <v>7</v>
+      </c>
+      <c r="P5" s="23" t="n">
+        <f aca="false">O5*H5</f>
+        <v>8855</v>
+      </c>
+      <c r="Q5" s="36" t="n">
+        <f aca="false">G5*(1-0.5)</f>
+        <v>6.325</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>370</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>374</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F6" s="31" t="n">
+        <v>141.55</v>
+      </c>
+      <c r="G6" s="32" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="H6" s="23" t="n">
+        <f aca="false">G6*100</f>
+        <v>655</v>
+      </c>
+      <c r="I6" s="31" t="n">
+        <v>133.45</v>
+      </c>
+      <c r="J6" s="33" t="n">
+        <f aca="false">I6/F6-1</f>
+        <v>-0.0572235959025081</v>
+      </c>
+      <c r="K6" s="32" t="n">
+        <v>8.45</v>
+      </c>
+      <c r="L6" s="34" t="n">
+        <f aca="false">IF(K6="","open",K6/G6)</f>
+        <v>1.29007633587786</v>
+      </c>
+      <c r="M6" s="7" t="n">
+        <v>0.443122516868418</v>
+      </c>
+      <c r="N6" s="7" t="n">
+        <v>0.568444856283021</v>
+      </c>
+      <c r="O6" s="35" t="n">
+        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H6)</f>
+        <v>15</v>
+      </c>
+      <c r="P6" s="23" t="n">
+        <f aca="false">O6*H6</f>
+        <v>9825</v>
+      </c>
+      <c r="Q6" s="36" t="n">
+        <f aca="false">G6*(1-0.5)</f>
+        <v>3.275</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F7" s="31" t="n">
+        <v>229.33</v>
+      </c>
+      <c r="G7" s="32" t="n">
+        <v>7.825</v>
+      </c>
+      <c r="H7" s="23" t="n">
+        <f aca="false">G7*100</f>
+        <v>782.5</v>
+      </c>
+      <c r="I7" s="31" t="n">
+        <v>237.825</v>
+      </c>
+      <c r="J7" s="33" t="n">
+        <f aca="false">I7/F7-1</f>
+        <v>0.0370426895739762</v>
+      </c>
+      <c r="K7" s="32" t="n">
+        <v>12.175</v>
+      </c>
+      <c r="L7" s="34" t="n">
+        <f aca="false">IF(K7="","open",K7/G7)</f>
+        <v>1.55591054313099</v>
+      </c>
+      <c r="M7" s="7" t="n">
+        <v>0.394779768673195</v>
+      </c>
+      <c r="N7" s="7" t="n">
+        <v>0.340953465060969</v>
+      </c>
+      <c r="O7" s="35" t="n">
+        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H7)</f>
+        <v>12</v>
+      </c>
+      <c r="P7" s="23" t="n">
+        <f aca="false">O7*H7</f>
+        <v>9390</v>
+      </c>
+      <c r="Q7" s="36" t="n">
+        <f aca="false">G7*(1-0.5)</f>
+        <v>3.9125</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>376</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F8" s="31" t="n">
+        <v>751.38</v>
+      </c>
+      <c r="G8" s="32" t="n">
+        <v>25.26</v>
+      </c>
+      <c r="H8" s="23" t="n">
+        <f aca="false">G8*100</f>
+        <v>2526</v>
+      </c>
+      <c r="I8" s="31" t="n">
+        <v>776.26</v>
+      </c>
+      <c r="J8" s="33" t="n">
+        <f aca="false">I8/F8-1</f>
+        <v>0.0331124065053634</v>
+      </c>
+      <c r="K8" s="32" t="n">
+        <v>48.74</v>
+      </c>
+      <c r="L8" s="34" t="n">
+        <f aca="false">IF(K8="","open",K8/G8)</f>
+        <v>1.92953285827395</v>
+      </c>
+      <c r="M8" s="7" t="n">
+        <v>0.368962735908992</v>
+      </c>
+      <c r="N8" s="7" t="n">
+        <v>0.194792627653838</v>
+      </c>
+      <c r="O8" s="35" t="n">
+        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H8)</f>
+        <v>3</v>
+      </c>
+      <c r="P8" s="23" t="n">
+        <f aca="false">O8*H8</f>
+        <v>7578</v>
+      </c>
+      <c r="Q8" s="36" t="n">
+        <f aca="false">G8*(1-0.5)</f>
+        <v>12.63</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>377</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F9" s="31" t="n">
+        <v>778.57</v>
+      </c>
+      <c r="G9" s="32" t="n">
+        <v>20.395</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <f aca="false">G9*100</f>
+        <v>2039.5</v>
+      </c>
+      <c r="I9" s="31" t="n">
+        <v>799.395</v>
+      </c>
+      <c r="J9" s="33" t="n">
+        <f aca="false">I9/F9-1</f>
+        <v>0.0267477555004687</v>
+      </c>
+      <c r="K9" s="32" t="n">
+        <v>55.605</v>
+      </c>
+      <c r="L9" s="34" t="n">
+        <f aca="false">IF(K9="","open",K9/G9)</f>
+        <v>2.72640353027703</v>
+      </c>
+      <c r="M9" s="7" t="n">
+        <v>0.363472788907844</v>
+      </c>
+      <c r="N9" s="7" t="n">
+        <v>0.133650255019125</v>
+      </c>
+      <c r="O9" s="35" t="n">
+        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H9)</f>
+        <v>4</v>
+      </c>
+      <c r="P9" s="23" t="n">
+        <f aca="false">O9*H9</f>
+        <v>8158</v>
+      </c>
+      <c r="Q9" s="36" t="n">
+        <f aca="false">G9*(1-0.5)</f>
+        <v>10.1975</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>379</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F10" s="31" t="n">
+        <v>141.55</v>
+      </c>
+      <c r="G10" s="32" t="n">
+        <v>10.15</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <f aca="false">G10*100</f>
+        <v>1015</v>
+      </c>
+      <c r="I10" s="31" t="n">
+        <v>124.85</v>
+      </c>
+      <c r="J10" s="33" t="n">
+        <f aca="false">I10/F10-1</f>
+        <v>-0.117979512539739</v>
+      </c>
+      <c r="K10" s="32"/>
+      <c r="L10" s="34" t="str">
+        <f aca="false">IF(K10="","open",K10/G10)</f>
+        <v>open</v>
+      </c>
+      <c r="M10" s="7" t="n">
+        <v>0.339881226108832</v>
+      </c>
+      <c r="N10" s="7" t="n">
+        <v>0.566607287616487</v>
+      </c>
+      <c r="O10" s="35" t="n">
+        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H10)</f>
+        <v>9</v>
+      </c>
+      <c r="P10" s="23" t="n">
+        <f aca="false">O10*H10</f>
+        <v>9135</v>
+      </c>
+      <c r="Q10" s="36" t="n">
+        <f aca="false">G10*(1-0.5)</f>
+        <v>5.075</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E11" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F11" s="31" t="n">
+        <v>168.79</v>
+      </c>
+      <c r="G11" s="32" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <f aca="false">G11*100</f>
+        <v>565</v>
+      </c>
+      <c r="I11" s="31" t="n">
+        <v>180.65</v>
+      </c>
+      <c r="J11" s="33" t="n">
+        <f aca="false">I11/F11-1</f>
+        <v>0.0702648261152912</v>
+      </c>
+      <c r="K11" s="32"/>
+      <c r="L11" s="34" t="str">
+        <f aca="false">IF(K11="","open",K11/G11)</f>
+        <v>open</v>
+      </c>
+      <c r="M11" s="7" t="n">
+        <v>0.289317614247436</v>
+      </c>
+      <c r="N11" s="7" t="n">
+        <v>0.278166458712079</v>
+      </c>
+      <c r="O11" s="35" t="n">
+        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H11)</f>
+        <v>17</v>
+      </c>
+      <c r="P11" s="23" t="n">
+        <f aca="false">O11*H11</f>
+        <v>9605</v>
+      </c>
+      <c r="Q11" s="36" t="n">
+        <f aca="false">G11*(1-0.5)</f>
+        <v>2.825</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E12" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F12" s="31" t="n">
+        <v>229.33</v>
+      </c>
+      <c r="G12" s="32" t="n">
+        <v>9.725</v>
+      </c>
+      <c r="H12" s="23" t="n">
+        <f aca="false">G12*100</f>
+        <v>972.5</v>
+      </c>
+      <c r="I12" s="31" t="n">
+        <v>249.725</v>
+      </c>
+      <c r="J12" s="33" t="n">
+        <f aca="false">I12/F12-1</f>
+        <v>0.0889329786770157</v>
+      </c>
+      <c r="K12" s="32"/>
+      <c r="L12" s="34" t="str">
+        <f aca="false">IF(K12="","open",K12/G12)</f>
+        <v>open</v>
+      </c>
+      <c r="M12" s="7" t="n">
+        <v>0.273762735822154</v>
+      </c>
+      <c r="N12" s="7" t="n">
+        <v>0.335245429054431</v>
+      </c>
+      <c r="O12" s="35" t="n">
+        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H12)</f>
+        <v>10</v>
+      </c>
+      <c r="P12" s="23" t="n">
+        <f aca="false">O12*H12</f>
+        <v>9725</v>
+      </c>
+      <c r="Q12" s="36" t="n">
+        <f aca="false">G12*(1-0.5)</f>
+        <v>4.8625</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E13" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F13" s="31" t="n">
+        <v>351.6</v>
+      </c>
+      <c r="G13" s="32" t="n">
+        <v>13.675</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <f aca="false">G13*100</f>
+        <v>1367.5</v>
+      </c>
+      <c r="I13" s="31" t="n">
+        <v>383.675</v>
+      </c>
+      <c r="J13" s="33" t="n">
+        <f aca="false">I13/F13-1</f>
+        <v>0.0912258248009101</v>
+      </c>
+      <c r="K13" s="32"/>
+      <c r="L13" s="34" t="str">
+        <f aca="false">IF(K13="","open",K13/G13)</f>
+        <v>open</v>
+      </c>
+      <c r="M13" s="7" t="n">
+        <v>0.263871389642364</v>
+      </c>
+      <c r="N13" s="7" t="n">
+        <v>0.324467860851498</v>
+      </c>
+      <c r="O13" s="35" t="n">
+        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H13)</f>
+        <v>7</v>
+      </c>
+      <c r="P13" s="23" t="n">
+        <f aca="false">O13*H13</f>
+        <v>9572.5</v>
+      </c>
+      <c r="Q13" s="36" t="n">
+        <f aca="false">G13*(1-0.5)</f>
+        <v>6.8375</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>384</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E14" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F14" s="31" t="n">
+        <v>384.5</v>
+      </c>
+      <c r="G14" s="32" t="n">
+        <v>5.525</v>
+      </c>
+      <c r="H14" s="23" t="n">
+        <f aca="false">G14*100</f>
+        <v>552.5</v>
+      </c>
+      <c r="I14" s="31" t="n">
+        <v>359.475</v>
+      </c>
+      <c r="J14" s="33" t="n">
+        <f aca="false">I14/F14-1</f>
+        <v>-0.0650845253576072</v>
+      </c>
+      <c r="K14" s="32"/>
+      <c r="L14" s="34" t="str">
+        <f aca="false">IF(K14="","open",K14/G14)</f>
+        <v>open</v>
+      </c>
+      <c r="M14" s="7" t="n">
+        <v>0.22652457613958</v>
+      </c>
+      <c r="N14" s="7" t="n">
+        <v>0.214702125013975</v>
+      </c>
+      <c r="O14" s="35" t="n">
+        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H14)</f>
+        <v>18</v>
+      </c>
+      <c r="P14" s="23" t="n">
+        <f aca="false">O14*H14</f>
+        <v>9945</v>
+      </c>
+      <c r="Q14" s="36" t="n">
+        <f aca="false">G14*(1-0.5)</f>
+        <v>2.7625</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E15" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F15" s="31" t="n">
+        <v>336.08</v>
+      </c>
+      <c r="G15" s="32" t="n">
+        <v>7.75</v>
+      </c>
+      <c r="H15" s="23" t="n">
+        <f aca="false">G15*100</f>
+        <v>775</v>
+      </c>
+      <c r="I15" s="31" t="n">
+        <v>362.75</v>
+      </c>
+      <c r="J15" s="33" t="n">
+        <f aca="false">I15/F15-1</f>
+        <v>0.0793561056891217</v>
+      </c>
+      <c r="K15" s="32"/>
+      <c r="L15" s="34" t="str">
+        <f aca="false">IF(K15="","open",K15/G15)</f>
+        <v>open</v>
+      </c>
+      <c r="M15" s="7" t="n">
+        <v>0.237030626911625</v>
+      </c>
+      <c r="N15" s="7" t="n">
+        <v>0.236173523215233</v>
+      </c>
+      <c r="O15" s="35" t="n">
+        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H15)</f>
+        <v>12</v>
+      </c>
+      <c r="P15" s="23" t="n">
+        <f aca="false">O15*H15</f>
+        <v>9300</v>
+      </c>
+      <c r="Q15" s="36" t="n">
+        <f aca="false">G15*(1-0.5)</f>
+        <v>3.875</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>386</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F16" s="31" t="n">
+        <v>751.38</v>
+      </c>
+      <c r="G16" s="32" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="H16" s="23" t="n">
+        <f aca="false">G16*100</f>
+        <v>1102</v>
+      </c>
+      <c r="I16" s="31" t="n">
+        <v>800.02</v>
+      </c>
+      <c r="J16" s="33" t="n">
+        <f aca="false">I16/F16-1</f>
+        <v>0.0647342223641831</v>
+      </c>
+      <c r="K16" s="32"/>
+      <c r="L16" s="34" t="str">
+        <f aca="false">IF(K16="","open",K16/G16)</f>
+        <v>open</v>
+      </c>
+      <c r="M16" s="7" t="n">
+        <v>0.224316324820298</v>
+      </c>
+      <c r="N16" s="7" t="n">
+        <v>0.174740994153321</v>
+      </c>
+      <c r="O16" s="35" t="n">
+        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H16)</f>
+        <v>9</v>
+      </c>
+      <c r="P16" s="23" t="n">
+        <f aca="false">O16*H16</f>
+        <v>9918</v>
+      </c>
+      <c r="Q16" s="36" t="n">
+        <f aca="false">G16*(1-0.5)</f>
+        <v>5.51</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>369</v>
+      </c>
+      <c r="E17" s="30" t="n">
+        <v>70</v>
+      </c>
+      <c r="F17" s="31" t="n">
+        <v>778.57</v>
+      </c>
+      <c r="G17" s="32" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="H17" s="23" t="n">
+        <f aca="false">G17*100</f>
+        <v>466</v>
+      </c>
+      <c r="I17" s="31" t="n">
+        <v>821.66</v>
+      </c>
+      <c r="J17" s="33" t="n">
+        <f aca="false">I17/F17-1</f>
+        <v>0.0553450556790012</v>
+      </c>
+      <c r="K17" s="32"/>
+      <c r="L17" s="34" t="str">
+        <f aca="false">IF(K17="","open",K17/G17)</f>
+        <v>open</v>
+      </c>
+      <c r="M17" s="7" t="n">
+        <v>0.171791316837144</v>
+      </c>
+      <c r="N17" s="7" t="n">
+        <v>0.114405791873116</v>
+      </c>
+      <c r="O17" s="35" t="n">
+        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H17)</f>
+        <v>21</v>
+      </c>
+      <c r="P17" s="23" t="n">
+        <f aca="false">O17*H17</f>
+        <v>9786</v>
+      </c>
+      <c r="Q17" s="36" t="n">
+        <f aca="false">G17*(1-0.5)</f>
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="9" t="s">
+        <v>388</v>
+      </c>
+      <c r="O19" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="P19" s="23" t="n">
+        <f aca="false">SUM(P2:P17)</f>
+        <v>149579</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O20" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="P20" s="23" t="n">
+        <f aca="false">Policy!$B$2*Policy!$B$10</f>
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O21" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="P21" s="0" t="str">
+        <f aca="false">IF(P19&lt;=P20,"Yes","No: pick fewer trades")</f>
+        <v>No: pick fewer trades</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -7919,71 +9165,71 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>346</v>
+        <v>393</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>348</v>
+        <v>395</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>349</v>
+        <v>396</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>350</v>
+        <v>397</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>351</v>
+        <v>398</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>352</v>
+        <v>399</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>353</v>
+        <v>400</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="30" t="s">
-        <v>354</v>
-      </c>
-      <c r="B2" s="30" t="s">
-        <v>66</v>
-      </c>
-      <c r="C2" s="30" t="s">
-        <v>71</v>
-      </c>
-      <c r="D2" s="30" t="n">
+      <c r="A2" s="37" t="s">
+        <v>401</v>
+      </c>
+      <c r="B2" s="37" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="D2" s="37" t="n">
         <v>65.08</v>
       </c>
-      <c r="E2" s="31" t="n">
+      <c r="E2" s="38" t="n">
         <v>0.029</v>
       </c>
-      <c r="F2" s="30" t="n">
+      <c r="F2" s="37" t="n">
         <v>55.59</v>
       </c>
-      <c r="G2" s="30" t="s">
-        <v>355</v>
-      </c>
-      <c r="H2" s="30" t="s">
-        <v>356</v>
-      </c>
-      <c r="I2" s="30" t="s">
-        <v>357</v>
-      </c>
-      <c r="J2" s="30" t="s">
-        <v>358</v>
-      </c>
-      <c r="K2" s="30"/>
+      <c r="G2" s="37" t="s">
+        <v>402</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>403</v>
+      </c>
+      <c r="I2" s="37" t="s">
+        <v>404</v>
+      </c>
+      <c r="J2" s="37" t="s">
+        <v>405</v>
+      </c>
+      <c r="K2" s="37"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/reports/2026-10-11/decision-book.xlsx
+++ b/reports/2026-10-11/decision-book.xlsx
@@ -1026,34 +1026,34 @@
     <t xml:space="preserve">Yield in target band but price in down-trend: stage in thirds (now, at 1.131 for 7% yield, and after trend repair).</t>
   </si>
   <si>
-    <t xml:space="preserve">Yield in target band but price in down-trend: stage in thirds (now, at 1.889 for 7% yield, and after trend repair).</t>
+    <t xml:space="preserve">Yield 4.97% below band; would reach 6% at 1.765.</t>
   </si>
   <si>
     <t xml:space="preserve">Yield 5.84% below band; would reach 6% at 2.016.</t>
   </si>
   <si>
-    <t xml:space="preserve">Yield 5.68% below band; would reach 6% at 0.903.</t>
+    <t xml:space="preserve">Yield 5.58% below band; would reach 6% at 0.888.</t>
   </si>
   <si>
     <t xml:space="preserve">Yield 4.75% below band; would reach 6% at 1.772.</t>
   </si>
   <si>
-    <t xml:space="preserve">Yield 4.36% below band; would reach 6% at 3.083.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yield 4.33% below band; would reach 6% at 53.000.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yield 4.12% below band; would reach 6% at 2.735.</t>
+    <t xml:space="preserve">Yield 3.86% below band; would reach 6% at 2.725.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yield 3.44% below band; would reach 6% at 42.083.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yield 3.84% below band; would reach 6% at 2.545.</t>
   </si>
   <si>
     <t xml:space="preserve">Yield 3.98% below band; would reach 6% at 26.500.</t>
   </si>
   <si>
-    <t xml:space="preserve">Yield 3.62% below band; would reach 6% at 17.500.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yield 2.30% below band; would reach 6% at 4.000.</t>
+    <t xml:space="preserve">Yield 3.18% below band; would reach 6% at 15.375.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yield 1.75% below band; would reach 6% at 3.042.</t>
   </si>
   <si>
     <t xml:space="preserve">Trailing cash = distributions with ex-date in the 365 days to the as-of date, from IBKR corporate actions, cross-checked to IBKR dividend yield.</t>
@@ -7441,7 +7441,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
         <v>281</v>
       </c>
@@ -7482,7 +7482,7 @@
         <v>-0.108786610878661</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>75</v>
+        <v>225</v>
       </c>
       <c r="M6" s="29" t="s">
         <v>317</v>

--- a/reports/2026-10-11/decision-book.xlsx
+++ b/reports/2026-10-11/decision-book.xlsx
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="406">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="817" uniqueCount="393">
   <si>
     <t xml:space="preserve">Global Investment Decision Book</t>
   </si>
@@ -183,6 +183,12 @@
     <t xml:space="preserve">Premium at risk per option trade</t>
   </si>
   <si>
+    <t xml:space="preserve">Gap allowance at the exit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exits close beyond the level (mean 2.3% since 2008); added to the distance when sizing</t>
+  </si>
+  <si>
     <t xml:space="preserve">Portfolio tilts this week</t>
   </si>
   <si>
@@ -192,7 +198,7 @@
     <t xml:space="preserve">Because: Long yields rising (bond prices down-trend)</t>
   </si>
   <si>
-    <t xml:space="preserve">Hedge or underweight non-USD assets for a USD-based portfolio; strong dollar is a headwind for HK/EM</t>
+    <t xml:space="preserve">Dollar strengthening: for a GBP-based portfolio unhedged US assets gain from the currency, so do not hedge USD exposure now; a strong dollar is a headwind for HK/EM</t>
   </si>
   <si>
     <t xml:space="preserve">Because: Dollar strengthening</t>
@@ -324,6 +330,15 @@
     <t xml:space="preserve">Exxon Mobil</t>
   </si>
   <si>
+    <t xml:space="preserve">SOXX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semiconductor ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semiconductors</t>
+  </si>
+  <si>
     <t xml:space="preserve">CPER</t>
   </si>
   <si>
@@ -396,9 +411,6 @@
     <t xml:space="preserve">Nvidia</t>
   </si>
   <si>
-    <t xml:space="preserve">Semiconductors</t>
-  </si>
-  <si>
     <t xml:space="preserve">CRWD</t>
   </si>
   <si>
@@ -411,7 +423,7 @@
     <t xml:space="preserve">Hold</t>
   </si>
   <si>
-    <t xml:space="preserve">Up-trend but 74% above 40-week average: hold, do not chase; add on pullback.</t>
+    <t xml:space="preserve">Up-trend but 73% above 40-week average: hold, do not chase; add on pullback.</t>
   </si>
   <si>
     <t xml:space="preserve">USO</t>
@@ -423,16 +435,7 @@
     <t xml:space="preserve">Crude oil</t>
   </si>
   <si>
-    <t xml:space="preserve">Up-trend but 25% above 40-week average: hold, do not chase; add on pullback.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SOXX</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Semiconductor ETF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Up-trend but 20% above 40-week average: hold, do not chase; add on pullback.</t>
+    <t xml:space="preserve">Up-trend but 24% above 40-week average: hold, do not chase; add on pullback.</t>
   </si>
   <si>
     <t xml:space="preserve">PANW</t>
@@ -441,7 +444,7 @@
     <t xml:space="preserve">Palo Alto Networks</t>
   </si>
   <si>
-    <t xml:space="preserve">Up-trend but 63% above 40-week average: hold, do not chase; add on pullback.</t>
+    <t xml:space="preserve">Up-trend but 61% above 40-week average: hold, do not chase; add on pullback.</t>
   </si>
   <si>
     <t xml:space="preserve">MSFT</t>
@@ -450,9 +453,6 @@
     <t xml:space="preserve">Microsoft</t>
   </si>
   <si>
-    <t xml:space="preserve">Up-trend but 23% above 40-week average: hold, do not chase; add on pullback.</t>
-  </si>
-  <si>
     <t xml:space="preserve">ANET</t>
   </si>
   <si>
@@ -705,6 +705,78 @@
     <t xml:space="preserve">Market infrastructure</t>
   </si>
   <si>
+    <t xml:space="preserve">823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Link REIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Property</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AstraZeneca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C2PU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parkway Life REIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Healthcare REIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XLP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consumer Staples Select ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avoid</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Price below 10- and 40-week averages (down-trend): no new money until trend repairs.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iShares Silver Trust</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Silver</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPDR Gold Shares</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gold</t>
+  </si>
+  <si>
+    <t xml:space="preserve">601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ping An A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GSK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NG.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">National Grid</t>
+  </si>
+  <si>
     <t xml:space="preserve">BA.</t>
   </si>
   <si>
@@ -714,114 +786,42 @@
     <t xml:space="preserve">Defence</t>
   </si>
   <si>
+    <t xml:space="preserve">1299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Z74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Singtel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Telecom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">XLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Communication Services Select ETF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CJLU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NetLink NBN Trust</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business trust</t>
+  </si>
+  <si>
     <t xml:space="preserve">XLRE</t>
   </si>
   <si>
     <t xml:space="preserve">Real Estate Select Sector ETF</t>
   </si>
   <si>
-    <t xml:space="preserve">Property</t>
-  </si>
-  <si>
-    <t xml:space="preserve">823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Link REIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AstraZeneca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C2PU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parkway Life REIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Healthcare REIT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XLP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consumer Staples Select ETF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avoid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Price below 10- and 40-week averages (down-trend): no new money until trend repairs.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLV</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iShares Silver Trust</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Silver</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPDR Gold Shares</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gold</t>
-  </si>
-  <si>
-    <t xml:space="preserve">601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ping An A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GSK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NG.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">National Grid</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Z74</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Singtel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Telecom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">XLC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Communication Services Select ETF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CJLU</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NetLink NBN Trust</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business trust</t>
-  </si>
-  <si>
     <t xml:space="preserve">600519</t>
   </si>
   <si>
@@ -1198,45 +1198,6 @@
   </si>
   <si>
     <t xml:space="preserve">Buy 140P / Sell 125P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy 230C / Sell 250C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy 751C / Sell 825C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy 779C / Sell 855C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Long put</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy 135P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Long call</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy 175C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy 240C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy 370C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy 365P</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy 355C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy 789C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Buy 817C</t>
   </si>
   <si>
     <t xml:space="preserve">Sleeve check</t>
@@ -2041,7 +2002,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2170,16 +2131,19 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="9" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="s">
         <v>36</v>
       </c>
+      <c r="B12" s="8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C14" s="2" t="s">
+      <c r="A14" s="9" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2229,6 +2193,14 @@
       </c>
       <c r="C20" s="2" t="s">
         <v>50</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -2269,84 +2241,84 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="Q1" s="5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="R1" s="5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="S1" s="5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C2" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G2" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H2" s="13" t="n">
         <v>65.08</v>
@@ -2358,24 +2330,24 @@
         <v>65.08</v>
       </c>
       <c r="K2" s="13" t="n">
-        <v>57.3121951219512</v>
+        <v>57.60375</v>
       </c>
       <c r="L2" s="14" t="n">
         <f aca="false">IF(K2="","",K2*(1-Policy!$B$7))</f>
-        <v>55.5928292682927</v>
+        <v>55.8756375</v>
       </c>
       <c r="M2" s="14"/>
       <c r="N2" s="15" t="n">
         <f aca="false">IF(L2="","",H2/L2-1)</f>
-        <v>0.170654576436863</v>
+        <v>0.1647294404471</v>
       </c>
       <c r="O2" s="15" t="n">
-        <f aca="false">IF(AND(F2="Accumulate",N2&lt;&gt;"",N2&gt;0),MIN(Policy!$B$4/N2,IF(E2="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
-        <v>0.0292989505725319</v>
+        <f aca="false">IF(AND(F2="Accumulate",N2&lt;&gt;"",N2&gt;0),MIN(Policy!$B$4/(N2+Policy!$B$12),IF(E2="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <v>0.0270666115151895</v>
       </c>
       <c r="P2" s="16" t="n">
         <f aca="false">IF(O2="","",O2*Policy!$B$3*Policy!$B$2)</f>
-        <v>29298.9505725319</v>
+        <v>27066.6115151895</v>
       </c>
       <c r="Q2" s="17" t="n">
         <v>0.181554103122731</v>
@@ -2389,25 +2361,25 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F3" s="11" t="s">
         <v>77</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="G3" s="12" t="s">
         <v>78</v>
-      </c>
-      <c r="C3" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F3" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>76</v>
       </c>
       <c r="H3" s="13" t="n">
         <v>37.954</v>
@@ -2419,24 +2391,24 @@
         <v>37.954</v>
       </c>
       <c r="K3" s="13" t="n">
-        <v>31.977512195122</v>
+        <v>32.08545</v>
       </c>
       <c r="L3" s="14" t="n">
         <f aca="false">IF(K3="","",K3*(1-Policy!$B$7))</f>
-        <v>31.0181868292683</v>
+        <v>31.1228865</v>
       </c>
       <c r="M3" s="14"/>
       <c r="N3" s="15" t="n">
         <f aca="false">IF(L3="","",H3/L3-1)</f>
-        <v>0.223604726121102</v>
+        <v>0.219488430162158</v>
       </c>
       <c r="O3" s="15" t="n">
-        <f aca="false">IF(AND(F3="Accumulate",N3&lt;&gt;"",N3&gt;0),MIN(Policy!$B$4/N3,IF(E3="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
-        <v>0.0223608869398049</v>
+        <f aca="false">IF(AND(F3="Accumulate",N3&lt;&gt;"",N3&gt;0),MIN(Policy!$B$4/(N3+Policy!$B$12),IF(E3="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <v>0.0208778352950683</v>
       </c>
       <c r="P3" s="16" t="n">
         <f aca="false">IF(O3="","",O3*Policy!$B$3*Policy!$B$2)</f>
-        <v>22360.8869398049</v>
+        <v>20877.8352950683</v>
       </c>
       <c r="Q3" s="17" t="n">
         <v>0.248322589133009</v>
@@ -2450,25 +2422,25 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="10" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B4" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>80</v>
-      </c>
       <c r="F4" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H4" s="13" t="n">
         <v>168.94</v>
@@ -2480,24 +2452,24 @@
         <v>168.94</v>
       </c>
       <c r="K4" s="13" t="n">
-        <v>150.664634146341</v>
+        <v>151.365</v>
       </c>
       <c r="L4" s="14" t="n">
         <f aca="false">IF(K4="","",K4*(1-Policy!$B$7))</f>
-        <v>146.144695121951</v>
+        <v>146.82405</v>
       </c>
       <c r="M4" s="14"/>
       <c r="N4" s="15" t="n">
         <f aca="false">IF(L4="","",H4/L4-1)</f>
-        <v>0.15597764160394</v>
+        <v>0.150628933066483</v>
       </c>
       <c r="O4" s="15" t="n">
-        <f aca="false">IF(AND(F4="Accumulate",N4&lt;&gt;"",N4&gt;0),MIN(Policy!$B$4/N4,IF(E4="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
-        <v>0.0320558763973111</v>
+        <f aca="false">IF(AND(F4="Accumulate",N4&lt;&gt;"",N4&gt;0),MIN(Policy!$B$4/(N4+Policy!$B$12),IF(E4="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <v>0.0293033538342047</v>
       </c>
       <c r="P4" s="16" t="n">
         <f aca="false">IF(O4="","",O4*Policy!$B$3*Policy!$B$2)</f>
-        <v>32055.8763973111</v>
+        <v>29303.3538342047</v>
       </c>
       <c r="Q4" s="17" t="n">
         <v>0.216445852534562</v>
@@ -2511,598 +2483,598 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H5" s="13" t="n">
-        <v>40.31</v>
+        <v>559.4</v>
       </c>
       <c r="I5" s="13" t="n">
-        <v>39.937</v>
+        <v>542.334</v>
       </c>
       <c r="J5" s="13" t="n">
-        <v>40.31</v>
+        <v>559.4</v>
       </c>
       <c r="K5" s="13" t="n">
-        <v>37.5685365853659</v>
+        <v>469.56475</v>
       </c>
       <c r="L5" s="14" t="n">
         <f aca="false">IF(K5="","",K5*(1-Policy!$B$7))</f>
-        <v>36.4414804878049</v>
+        <v>455.4778075</v>
       </c>
       <c r="M5" s="14"/>
       <c r="N5" s="15" t="n">
         <f aca="false">IF(L5="","",H5/L5-1)</f>
-        <v>0.106157034796918</v>
+        <v>0.228160825376767</v>
       </c>
       <c r="O5" s="15" t="n">
-        <f aca="false">IF(AND(F5="Accumulate",N5&lt;&gt;"",N5&gt;0),MIN(Policy!$B$4/N5,IF(E5="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
-        <v>0.0471000344872591</v>
+        <f aca="false">IF(AND(F5="Accumulate",N5&lt;&gt;"",N5&gt;0),MIN(Policy!$B$4/(N5+Policy!$B$12),IF(E5="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <v>0.0201482244121683</v>
       </c>
       <c r="P5" s="16" t="n">
         <f aca="false">IF(O5="","",O5*Policy!$B$3*Policy!$B$2)</f>
-        <v>47100.0344872591</v>
+        <v>20148.2244121683</v>
       </c>
       <c r="Q5" s="17" t="n">
-        <v>0.0610687022900764</v>
+        <v>-0.0377403928854028</v>
       </c>
       <c r="R5" s="17" t="n">
-        <v>0.331681532870829</v>
+        <v>1.05669326078165</v>
       </c>
       <c r="S5" s="18" t="n">
-        <v>1.03887131077321</v>
+        <v>1.32826909691167</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G6" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H6" s="13" t="n">
-        <v>198.78</v>
+        <v>40.31</v>
       </c>
       <c r="I6" s="13" t="n">
-        <v>190.639</v>
+        <v>39.937</v>
       </c>
       <c r="J6" s="13" t="n">
-        <v>198.78</v>
+        <v>40.31</v>
       </c>
       <c r="K6" s="13" t="n">
-        <v>166.832682926829</v>
+        <v>37.63325</v>
       </c>
       <c r="L6" s="14" t="n">
         <f aca="false">IF(K6="","",K6*(1-Policy!$B$7))</f>
-        <v>161.827702439024</v>
+        <v>36.5042525</v>
       </c>
       <c r="M6" s="14"/>
       <c r="N6" s="15" t="n">
         <f aca="false">IF(L6="","",H6/L6-1)</f>
-        <v>0.22834346038435</v>
+        <v>0.10425490838362</v>
       </c>
       <c r="O6" s="15" t="n">
-        <f aca="false">IF(AND(F6="Accumulate",N6&lt;&gt;"",N6&gt;0),MIN(Policy!$B$4/N6,IF(E6="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
-        <v>0.0218968390493161</v>
+        <f aca="false">IF(AND(F6="Accumulate",N6&lt;&gt;"",N6&gt;0),MIN(Policy!$B$4/(N6+Policy!$B$12),IF(E6="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <v>0.0402398590529978</v>
       </c>
       <c r="P6" s="16" t="n">
         <f aca="false">IF(O6="","",O6*Policy!$B$3*Policy!$B$2)</f>
-        <v>21896.8390493161</v>
+        <v>40239.8590529978</v>
       </c>
       <c r="Q6" s="17" t="n">
-        <v>0.0699752395306277</v>
+        <v>0.0610687022900764</v>
       </c>
       <c r="R6" s="17" t="n">
-        <v>0.39489842461668</v>
+        <v>0.331681532870829</v>
       </c>
       <c r="S6" s="18" t="n">
-        <v>0.978126317423683</v>
+        <v>1.03887131077321</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="10" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G7" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H7" s="13" t="n">
-        <v>778.57</v>
+        <v>198.78</v>
       </c>
       <c r="I7" s="13" t="n">
-        <v>770.04</v>
+        <v>190.639</v>
       </c>
       <c r="J7" s="13" t="n">
-        <v>778.57</v>
+        <v>198.78</v>
       </c>
       <c r="K7" s="13" t="n">
-        <v>723.379512195122</v>
+        <v>167.396</v>
       </c>
       <c r="L7" s="14" t="n">
         <f aca="false">IF(K7="","",K7*(1-Policy!$B$7))</f>
-        <v>701.678126829268</v>
+        <v>162.37412</v>
       </c>
       <c r="M7" s="14"/>
       <c r="N7" s="15" t="n">
         <f aca="false">IF(L7="","",H7/L7-1)</f>
-        <v>0.109582827553981</v>
+        <v>0.224209867927229</v>
       </c>
       <c r="O7" s="15" t="n">
-        <f aca="false">IF(AND(F7="Accumulate",N7&lt;&gt;"",N7&gt;0),MIN(Policy!$B$4/N7,IF(E7="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
-        <v>0.0456275870189332</v>
+        <f aca="false">IF(AND(F7="Accumulate",N7&lt;&gt;"",N7&gt;0),MIN(Policy!$B$4/(N7+Policy!$B$12),IF(E7="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <v>0.0204741931292061</v>
       </c>
       <c r="P7" s="16" t="n">
         <f aca="false">IF(O7="","",O7*Policy!$B$3*Policy!$B$2)</f>
-        <v>45627.5870189332</v>
+        <v>20474.1931292061</v>
       </c>
       <c r="Q7" s="17" t="n">
-        <v>0.0312868401880919</v>
+        <v>0.0699752395306277</v>
       </c>
       <c r="R7" s="17" t="n">
-        <v>0.192260573948731</v>
+        <v>0.39489842461668</v>
       </c>
       <c r="S7" s="18" t="n">
-        <v>0.928004262194192</v>
+        <v>0.978126317423683</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="10" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C8" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G8" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H8" s="13" t="n">
-        <v>336.64</v>
+        <v>778.57</v>
       </c>
       <c r="I8" s="13" t="n">
-        <v>324.808</v>
+        <v>770.04</v>
       </c>
       <c r="J8" s="13" t="n">
-        <v>336.64</v>
+        <v>778.57</v>
       </c>
       <c r="K8" s="13" t="n">
-        <v>291.236097560976</v>
+        <v>724.38475</v>
       </c>
       <c r="L8" s="14" t="n">
         <f aca="false">IF(K8="","",K8*(1-Policy!$B$7))</f>
-        <v>282.499014634146</v>
+        <v>702.6532075</v>
       </c>
       <c r="M8" s="14"/>
       <c r="N8" s="15" t="n">
         <f aca="false">IF(L8="","",H8/L8-1)</f>
-        <v>0.191650174199615</v>
+        <v>0.108043045544626</v>
       </c>
       <c r="O8" s="15" t="n">
-        <f aca="false">IF(AND(F8="Accumulate",N8&lt;&gt;"",N8&gt;0),MIN(Policy!$B$4/N8,IF(E8="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
-        <v>0.0260892014363223</v>
+        <f aca="false">IF(AND(F8="Accumulate",N8&lt;&gt;"",N8&gt;0),MIN(Policy!$B$4/(N8+Policy!$B$12),IF(E8="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <v>0.0390493679585072</v>
       </c>
       <c r="P8" s="16" t="n">
         <f aca="false">IF(O8="","",O8*Policy!$B$3*Policy!$B$2)</f>
-        <v>26089.2014363223</v>
+        <v>39049.3679585072</v>
       </c>
       <c r="Q8" s="17" t="n">
-        <v>0.0676138525941901</v>
+        <v>0.0312868401880919</v>
       </c>
       <c r="R8" s="17" t="n">
-        <v>0.372528234190892</v>
+        <v>0.192260573948731</v>
       </c>
       <c r="S8" s="18" t="n">
-        <v>0.919019461628056</v>
+        <v>0.928004262194192</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C9" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G9" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H9" s="13" t="n">
-        <v>751.27</v>
+        <v>336.64</v>
       </c>
       <c r="I9" s="13" t="n">
-        <v>728.461</v>
+        <v>324.808</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>751.27</v>
+        <v>336.64</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>673.028048780488</v>
+        <v>291.74175</v>
       </c>
       <c r="L9" s="14" t="n">
         <f aca="false">IF(K9="","",K9*(1-Policy!$B$7))</f>
-        <v>652.837207317073</v>
+        <v>282.9894975</v>
       </c>
       <c r="M9" s="14"/>
       <c r="N9" s="15" t="n">
         <f aca="false">IF(L9="","",H9/L9-1)</f>
-        <v>0.150776934248969</v>
+        <v>0.189584783088991</v>
       </c>
       <c r="O9" s="15" t="n">
-        <f aca="false">IF(AND(F9="Accumulate",N9&lt;&gt;"",N9&gt;0),MIN(Policy!$B$4/N9,IF(E9="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
-        <v>0.0331615709319556</v>
+        <f aca="false">IF(AND(F9="Accumulate",N9&lt;&gt;"",N9&gt;0),MIN(Policy!$B$4/(N9+Policy!$B$12),IF(E9="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <v>0.0238566938224565</v>
       </c>
       <c r="P9" s="16" t="n">
         <f aca="false">IF(O9="","",O9*Policy!$B$3*Policy!$B$2)</f>
-        <v>33161.5709319556</v>
+        <v>23856.6938224565</v>
       </c>
       <c r="Q9" s="17" t="n">
-        <v>0.0355060578076112</v>
+        <v>0.0676138525941901</v>
       </c>
       <c r="R9" s="17" t="n">
-        <v>0.274418999151824</v>
+        <v>0.372528234190892</v>
       </c>
       <c r="S9" s="18" t="n">
-        <v>0.845404513958884</v>
+        <v>0.919019461628056</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G10" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H10" s="13" t="n">
-        <v>170.81</v>
+        <v>751.27</v>
       </c>
       <c r="I10" s="13" t="n">
-        <v>169.172</v>
+        <v>728.461</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>170.81</v>
+        <v>751.27</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>157.159512195122</v>
+        <v>674.52575</v>
       </c>
       <c r="L10" s="14" t="n">
         <f aca="false">IF(K10="","",K10*(1-Policy!$B$7))</f>
-        <v>152.444726829268</v>
+        <v>654.2899775</v>
       </c>
       <c r="M10" s="14"/>
       <c r="N10" s="15" t="n">
         <f aca="false">IF(L10="","",H10/L10-1)</f>
-        <v>0.120471685395193</v>
+        <v>0.148221776024378</v>
       </c>
       <c r="O10" s="15" t="n">
-        <f aca="false">IF(AND(F10="Accumulate",N10&lt;&gt;"",N10&gt;0),MIN(Policy!$B$4/N10,IF(E10="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
-        <v>0.0415035282655678</v>
+        <f aca="false">IF(AND(F10="Accumulate",N10&lt;&gt;"",N10&gt;0),MIN(Policy!$B$4/(N10+Policy!$B$12),IF(E10="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <v>0.0297226680050949</v>
       </c>
       <c r="P10" s="16" t="n">
         <f aca="false">IF(O10="","",O10*Policy!$B$3*Policy!$B$2)</f>
-        <v>41503.5282655678</v>
+        <v>29722.6680050949</v>
       </c>
       <c r="Q10" s="17" t="n">
-        <v>0.0619870678935588</v>
+        <v>0.0355060578076112</v>
       </c>
       <c r="R10" s="17" t="n">
-        <v>0.201956231088593</v>
+        <v>0.274418999151824</v>
       </c>
       <c r="S10" s="18" t="n">
-        <v>0.825869386805188</v>
+        <v>0.845404513958884</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="10" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G11" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H11" s="13" t="n">
-        <v>351.66</v>
+        <v>170.81</v>
       </c>
       <c r="I11" s="13" t="n">
-        <v>345.719</v>
+        <v>169.172</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>351.66</v>
+        <v>170.81</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>340.178780487805</v>
+        <v>157.20075</v>
       </c>
       <c r="L11" s="14" t="n">
         <f aca="false">IF(K11="","",K11*(1-Policy!$B$7))</f>
-        <v>329.973417073171</v>
+        <v>152.4847275</v>
       </c>
       <c r="M11" s="14"/>
       <c r="N11" s="15" t="n">
         <f aca="false">IF(L11="","",H11/L11-1)</f>
-        <v>0.0657222121684438</v>
+        <v>0.120177756818302</v>
       </c>
       <c r="O11" s="15" t="n">
-        <f aca="false">IF(AND(F11="Accumulate",N11&lt;&gt;"",N11&gt;0),MIN(Policy!$B$4/N11,IF(E11="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
-        <v>0.0760777800233683</v>
+        <f aca="false">IF(AND(F11="Accumulate",N11&lt;&gt;"",N11&gt;0),MIN(Policy!$B$4/(N11+Policy!$B$12),IF(E11="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <v>0.0356689970897522</v>
       </c>
       <c r="P11" s="16" t="n">
         <f aca="false">IF(O11="","",O11*Policy!$B$3*Policy!$B$2)</f>
-        <v>76077.7800233683</v>
+        <v>35668.9970897522</v>
       </c>
       <c r="Q11" s="17" t="n">
-        <v>-0.0154543927431546</v>
+        <v>0.0619870678935588</v>
       </c>
       <c r="R11" s="17" t="n">
-        <v>0.486494483662341</v>
+        <v>0.201956231088593</v>
       </c>
       <c r="S11" s="18" t="n">
-        <v>0.697454994270508</v>
+        <v>0.825869386805188</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="10" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C12" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G12" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H12" s="13" t="n">
-        <v>229.28</v>
+        <v>351.66</v>
       </c>
       <c r="I12" s="13" t="n">
-        <v>224.061</v>
+        <v>345.719</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>229.28</v>
+        <v>351.66</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>202.048292682927</v>
+        <v>340.8045</v>
       </c>
       <c r="L12" s="14" t="n">
         <f aca="false">IF(K12="","",K12*(1-Policy!$B$7))</f>
-        <v>195.986843902439</v>
+        <v>330.580365</v>
       </c>
       <c r="M12" s="14"/>
       <c r="N12" s="15" t="n">
         <f aca="false">IF(L12="","",H12/L12-1)</f>
-        <v>0.169874443787329</v>
+        <v>0.0637655385249514</v>
       </c>
       <c r="O12" s="15" t="n">
-        <f aca="false">IF(AND(F12="Accumulate",N12&lt;&gt;"",N12&gt;0),MIN(Policy!$B$4/N12,IF(E12="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
-        <v>0.0294335032894039</v>
+        <f aca="false">IF(AND(F12="Accumulate",N12&lt;&gt;"",N12&gt;0),MIN(Policy!$B$4/(N12+Policy!$B$12),IF(E12="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <v>0.0596904178979359</v>
       </c>
       <c r="P12" s="16" t="n">
         <f aca="false">IF(O12="","",O12*Policy!$B$3*Policy!$B$2)</f>
-        <v>29433.5032894039</v>
+        <v>59690.4178979359</v>
       </c>
       <c r="Q12" s="17" t="n">
-        <v>0.086841107318923</v>
+        <v>-0.0154543927431546</v>
       </c>
       <c r="R12" s="17" t="n">
-        <v>0.251801703428696</v>
+        <v>0.486494483662341</v>
       </c>
       <c r="S12" s="18" t="n">
-        <v>0.522876372428729</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.697454994270508</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="10" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C13" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F13" s="19" t="s">
-        <v>111</v>
+        <v>82</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>77</v>
       </c>
       <c r="G13" s="12" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="H13" s="13" t="n">
-        <v>275.04</v>
+        <v>229.28</v>
       </c>
       <c r="I13" s="13" t="n">
-        <v>229.642</v>
+        <v>224.061</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>275.04</v>
+        <v>229.28</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>157.854756097561</v>
+        <v>202.37825</v>
       </c>
       <c r="L13" s="14" t="n">
         <f aca="false">IF(K13="","",K13*(1-Policy!$B$7))</f>
-        <v>153.119113414634</v>
+        <v>196.3069025</v>
       </c>
       <c r="M13" s="14"/>
       <c r="N13" s="15" t="n">
         <f aca="false">IF(L13="","",H13/L13-1)</f>
-        <v>0.796248645035019</v>
-      </c>
-      <c r="O13" s="15" t="str">
-        <f aca="false">IF(AND(F13="Accumulate",N13&lt;&gt;"",N13&gt;0),MIN(Policy!$B$4/N13,IF(E13="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
-        <v/>
-      </c>
-      <c r="P13" s="16" t="str">
+        <v>0.167967081544675</v>
+      </c>
+      <c r="O13" s="15" t="n">
+        <f aca="false">IF(AND(F13="Accumulate",N13&lt;&gt;"",N13&gt;0),MIN(Policy!$B$4/(N13+Policy!$B$12),IF(E13="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <v>0.0266004023625362</v>
+      </c>
+      <c r="P13" s="16" t="n">
         <f aca="false">IF(O13="","",O13*Policy!$B$3*Policy!$B$2)</f>
-        <v/>
+        <v>26600.4023625362</v>
       </c>
       <c r="Q13" s="17" t="n">
-        <v>0.469387755102041</v>
+        <v>0.086841107318923</v>
       </c>
       <c r="R13" s="17" t="n">
-        <v>1.27000928505107</v>
+        <v>0.251801703428696</v>
       </c>
       <c r="S13" s="18" t="n">
-        <v>1.59094390312974</v>
+        <v>0.522876372428729</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="10" t="s">
+      <c r="C14" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" s="10" t="s">
+      <c r="E14" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F14" s="19" t="s">
         <v>115</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>111</v>
       </c>
       <c r="G14" s="12" t="s">
         <v>116</v>
       </c>
       <c r="H14" s="13" t="n">
-        <v>148.2</v>
+        <v>275.04</v>
       </c>
       <c r="I14" s="13" t="n">
-        <v>140.35</v>
+        <v>229.642</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>148.2</v>
+        <v>275.04</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>118.189512195122</v>
+        <v>158.96625</v>
       </c>
       <c r="L14" s="14" t="n">
         <f aca="false">IF(K14="","",K14*(1-Policy!$B$7))</f>
-        <v>114.643826829268</v>
+        <v>154.1972625</v>
       </c>
       <c r="M14" s="14"/>
       <c r="N14" s="15" t="n">
         <f aca="false">IF(L14="","",H14/L14-1)</f>
-        <v>0.292699346304139</v>
+        <v>0.783689253238202</v>
       </c>
       <c r="O14" s="15" t="str">
-        <f aca="false">IF(AND(F14="Accumulate",N14&lt;&gt;"",N14&gt;0),MIN(Policy!$B$4/N14,IF(E14="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F14="Accumulate",N14&lt;&gt;"",N14&gt;0),MIN(Policy!$B$4/(N14+Policy!$B$12),IF(E14="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P14" s="16" t="str">
@@ -3110,13 +3082,13 @@
         <v/>
       </c>
       <c r="Q14" s="17" t="n">
-        <v>0.363385464581417</v>
+        <v>0.469387755102041</v>
       </c>
       <c r="R14" s="17" t="n">
-        <v>1.13575443147428</v>
+        <v>1.27000928505107</v>
       </c>
       <c r="S14" s="18" t="n">
-        <v>1.36956073852849</v>
+        <v>1.59094390312974</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3127,43 +3099,43 @@
         <v>118</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F15" s="19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H15" s="13" t="n">
-        <v>559.4</v>
+        <v>148.2</v>
       </c>
       <c r="I15" s="13" t="n">
-        <v>542.334</v>
+        <v>140.35</v>
       </c>
       <c r="J15" s="13" t="n">
-        <v>559.4</v>
+        <v>148.2</v>
       </c>
       <c r="K15" s="13" t="n">
-        <v>465.762926829268</v>
+        <v>119.42025</v>
       </c>
       <c r="L15" s="14" t="n">
         <f aca="false">IF(K15="","",K15*(1-Policy!$B$7))</f>
-        <v>451.79003902439</v>
+        <v>115.8376425</v>
       </c>
       <c r="M15" s="14"/>
       <c r="N15" s="15" t="n">
         <f aca="false">IF(L15="","",H15/L15-1)</f>
-        <v>0.238185775870548</v>
+        <v>0.279376865771418</v>
       </c>
       <c r="O15" s="15" t="str">
-        <f aca="false">IF(AND(F15="Accumulate",N15&lt;&gt;"",N15&gt;0),MIN(Policy!$B$4/N15,IF(E15="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F15="Accumulate",N15&lt;&gt;"",N15&gt;0),MIN(Policy!$B$4/(N15+Policy!$B$12),IF(E15="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P15" s="16" t="str">
@@ -3171,36 +3143,36 @@
         <v/>
       </c>
       <c r="Q15" s="17" t="n">
-        <v>-0.0377403928854028</v>
+        <v>0.363385464581417</v>
       </c>
       <c r="R15" s="17" t="n">
-        <v>1.05669326078165</v>
+        <v>1.13575443147428</v>
       </c>
       <c r="S15" s="18" t="n">
-        <v>1.32826909691167</v>
+        <v>1.36956073852849</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C16" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H16" s="13" t="n">
         <v>418.78</v>
@@ -3212,19 +3184,19 @@
         <v>418.78</v>
       </c>
       <c r="K16" s="13" t="n">
-        <v>257.372682926829</v>
+        <v>259.32275</v>
       </c>
       <c r="L16" s="14" t="n">
         <f aca="false">IF(K16="","",K16*(1-Policy!$B$7))</f>
-        <v>249.651502439024</v>
+        <v>251.5430675</v>
       </c>
       <c r="M16" s="14"/>
       <c r="N16" s="15" t="n">
         <f aca="false">IF(L16="","",H16/L16-1)</f>
-        <v>0.677458360589214</v>
+        <v>0.664844132506256</v>
       </c>
       <c r="O16" s="15" t="str">
-        <f aca="false">IF(AND(F16="Accumulate",N16&lt;&gt;"",N16&gt;0),MIN(Policy!$B$4/N16,IF(E16="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F16="Accumulate",N16&lt;&gt;"",N16&gt;0),MIN(Policy!$B$4/(N16+Policy!$B$12),IF(E16="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P16" s="16" t="str">
@@ -3243,25 +3215,25 @@
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C17" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H17" s="13" t="n">
         <v>535.07</v>
@@ -3273,19 +3245,19 @@
         <v>535.07</v>
       </c>
       <c r="K17" s="13" t="n">
-        <v>433.697073170732</v>
+        <v>432.716</v>
       </c>
       <c r="L17" s="14" t="n">
         <f aca="false">IF(K17="","",K17*(1-Policy!$B$7))</f>
-        <v>420.68616097561</v>
+        <v>419.73452</v>
       </c>
       <c r="M17" s="14"/>
       <c r="N17" s="15" t="n">
         <f aca="false">IF(L17="","",H17/L17-1)</f>
-        <v>0.271898269149438</v>
+        <v>0.274781974091624</v>
       </c>
       <c r="O17" s="15" t="str">
-        <f aca="false">IF(AND(F17="Accumulate",N17&lt;&gt;"",N17&gt;0),MIN(Policy!$B$4/N17,IF(E17="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F17="Accumulate",N17&lt;&gt;"",N17&gt;0),MIN(Policy!$B$4/(N17+Policy!$B$12),IF(E17="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P17" s="16" t="str">
@@ -3310,16 +3282,16 @@
         <v>127</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D18" s="10" t="s">
         <v>128</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F18" s="19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>129</v>
@@ -3334,19 +3306,19 @@
         <v>216.74</v>
       </c>
       <c r="K18" s="13" t="n">
-        <v>161.534878048781</v>
+        <v>162.23325</v>
       </c>
       <c r="L18" s="14" t="n">
         <f aca="false">IF(K18="","",K18*(1-Policy!$B$7))</f>
-        <v>156.688831707317</v>
+        <v>157.3662525</v>
       </c>
       <c r="M18" s="14"/>
       <c r="N18" s="15" t="n">
         <f aca="false">IF(L18="","",H18/L18-1)</f>
-        <v>0.383251107550881</v>
+        <v>0.377296571258186</v>
       </c>
       <c r="O18" s="15" t="str">
-        <f aca="false">IF(AND(F18="Accumulate",N18&lt;&gt;"",N18&gt;0),MIN(Policy!$B$4/N18,IF(E18="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F18="Accumulate",N18&lt;&gt;"",N18&gt;0),MIN(Policy!$B$4/(N18+Policy!$B$12),IF(E18="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P18" s="16" t="str">
@@ -3377,10 +3349,10 @@
         <v>133</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F19" s="19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G19" s="12" t="s">
         <v>134</v>
@@ -3395,19 +3367,19 @@
         <v>41.42</v>
       </c>
       <c r="K19" s="13" t="n">
-        <v>39.1548780487805</v>
+        <v>39.09125</v>
       </c>
       <c r="L19" s="14" t="n">
         <f aca="false">IF(K19="","",K19*(1-Policy!$B$7))</f>
-        <v>37.9802317073171</v>
+        <v>37.9185125</v>
       </c>
       <c r="M19" s="14"/>
       <c r="N19" s="15" t="n">
         <f aca="false">IF(L19="","",H19/L19-1)</f>
-        <v>0.0905673330060344</v>
+        <v>0.0923424277257712</v>
       </c>
       <c r="O19" s="15" t="str">
-        <f aca="false">IF(AND(F19="Accumulate",N19&lt;&gt;"",N19&gt;0),MIN(Policy!$B$4/N19,IF(E19="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F19="Accumulate",N19&lt;&gt;"",N19&gt;0),MIN(Policy!$B$4/(N19+Policy!$B$12),IF(E19="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P19" s="16" t="str">
@@ -3432,16 +3404,16 @@
         <v>136</v>
       </c>
       <c r="C20" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D20" s="10" t="s">
         <v>137</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G20" s="12" t="s">
         <v>134</v>
@@ -3456,19 +3428,19 @@
         <v>262.43</v>
       </c>
       <c r="K20" s="13" t="n">
-        <v>242.595365853659</v>
+        <v>242.99775</v>
       </c>
       <c r="L20" s="14" t="n">
         <f aca="false">IF(K20="","",K20*(1-Policy!$B$7))</f>
-        <v>235.317504878049</v>
+        <v>235.7078175</v>
       </c>
       <c r="M20" s="14"/>
       <c r="N20" s="15" t="n">
         <f aca="false">IF(L20="","",H20/L20-1)</f>
-        <v>0.11521665222484</v>
+        <v>0.113369945822862</v>
       </c>
       <c r="O20" s="15" t="str">
-        <f aca="false">IF(AND(F20="Accumulate",N20&lt;&gt;"",N20&gt;0),MIN(Policy!$B$4/N20,IF(E20="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F20="Accumulate",N20&lt;&gt;"",N20&gt;0),MIN(Policy!$B$4/(N20+Policy!$B$12),IF(E20="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P20" s="16" t="str">
@@ -3493,16 +3465,16 @@
         <v>139</v>
       </c>
       <c r="C21" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F21" s="19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G21" s="12" t="s">
         <v>140</v>
@@ -3517,19 +3489,19 @@
         <v>112.67</v>
       </c>
       <c r="K21" s="13" t="n">
-        <v>93.3282926829268</v>
+        <v>93.096</v>
       </c>
       <c r="L21" s="14" t="n">
         <f aca="false">IF(K21="","",K21*(1-Policy!$B$7))</f>
-        <v>90.528443902439</v>
+        <v>90.30312</v>
       </c>
       <c r="M21" s="14"/>
       <c r="N21" s="15" t="n">
         <f aca="false">IF(L21="","",H21/L21-1)</f>
-        <v>0.244581207221706</v>
+        <v>0.247686680150143</v>
       </c>
       <c r="O21" s="15" t="str">
-        <f aca="false">IF(AND(F21="Accumulate",N21&lt;&gt;"",N21&gt;0),MIN(Policy!$B$4/N21,IF(E21="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F21="Accumulate",N21&lt;&gt;"",N21&gt;0),MIN(Policy!$B$4/(N21+Policy!$B$12),IF(E21="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P21" s="16" t="str">
@@ -3560,10 +3532,10 @@
         <v>143</v>
       </c>
       <c r="E22" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F22" s="19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G22" s="12" t="s">
         <v>134</v>
@@ -3578,19 +3550,19 @@
         <v>28.99</v>
       </c>
       <c r="K22" s="13" t="n">
-        <v>27.4034146341463</v>
+        <v>27.3975</v>
       </c>
       <c r="L22" s="14" t="n">
         <f aca="false">IF(K22="","",K22*(1-Policy!$B$7))</f>
-        <v>26.581312195122</v>
+        <v>26.575575</v>
       </c>
       <c r="M22" s="14"/>
       <c r="N22" s="15" t="n">
         <f aca="false">IF(L22="","",H22/L22-1)</f>
-        <v>0.0906158351851447</v>
+        <v>0.0908512797935697</v>
       </c>
       <c r="O22" s="15" t="str">
-        <f aca="false">IF(AND(F22="Accumulate",N22&lt;&gt;"",N22&gt;0),MIN(Policy!$B$4/N22,IF(E22="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F22="Accumulate",N22&lt;&gt;"",N22&gt;0),MIN(Policy!$B$4/(N22+Policy!$B$12),IF(E22="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P22" s="16" t="str">
@@ -3615,16 +3587,16 @@
         <v>145</v>
       </c>
       <c r="C23" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F23" s="19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G23" s="12" t="s">
         <v>134</v>
@@ -3639,19 +3611,19 @@
         <v>718.67</v>
       </c>
       <c r="K23" s="13" t="n">
-        <v>626.867804878049</v>
+        <v>626.27925</v>
       </c>
       <c r="L23" s="14" t="n">
         <f aca="false">IF(K23="","",K23*(1-Policy!$B$7))</f>
-        <v>608.061770731707</v>
+        <v>607.4908725</v>
       </c>
       <c r="M23" s="14"/>
       <c r="N23" s="15" t="n">
         <f aca="false">IF(L23="","",H23/L23-1)</f>
-        <v>0.181902948996766</v>
+        <v>0.183013659188764</v>
       </c>
       <c r="O23" s="15" t="str">
-        <f aca="false">IF(AND(F23="Accumulate",N23&lt;&gt;"",N23&gt;0),MIN(Policy!$B$4/N23,IF(E23="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F23="Accumulate",N23&lt;&gt;"",N23&gt;0),MIN(Policy!$B$4/(N23+Policy!$B$12),IF(E23="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P23" s="16" t="str">
@@ -3676,19 +3648,19 @@
         <v>147</v>
       </c>
       <c r="C24" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F24" s="19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="H24" s="13" t="n">
         <v>140.86</v>
@@ -3700,19 +3672,19 @@
         <v>140.86</v>
       </c>
       <c r="K24" s="13" t="n">
-        <v>114.334634146342</v>
+        <v>113.50675</v>
       </c>
       <c r="L24" s="14" t="n">
         <f aca="false">IF(K24="","",K24*(1-Policy!$B$7))</f>
-        <v>110.904595121951</v>
+        <v>110.1015475</v>
       </c>
       <c r="M24" s="14"/>
       <c r="N24" s="15" t="n">
         <f aca="false">IF(L24="","",H24/L24-1)</f>
-        <v>0.270100664856219</v>
+        <v>0.279364397671159</v>
       </c>
       <c r="O24" s="15" t="str">
-        <f aca="false">IF(AND(F24="Accumulate",N24&lt;&gt;"",N24&gt;0),MIN(Policy!$B$4/N24,IF(E24="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F24="Accumulate",N24&lt;&gt;"",N24&gt;0),MIN(Policy!$B$4/(N24+Policy!$B$12),IF(E24="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P24" s="16" t="str">
@@ -3737,16 +3709,16 @@
         <v>149</v>
       </c>
       <c r="C25" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D25" s="10" t="s">
         <v>150</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F25" s="19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G25" s="12" t="s">
         <v>134</v>
@@ -3761,19 +3733,19 @@
         <v>27.22</v>
       </c>
       <c r="K25" s="13" t="n">
-        <v>25.6421951219512</v>
+        <v>25.537</v>
       </c>
       <c r="L25" s="14" t="n">
         <f aca="false">IF(K25="","",K25*(1-Policy!$B$7))</f>
-        <v>24.8729292682927</v>
+        <v>24.77089</v>
       </c>
       <c r="M25" s="14"/>
       <c r="N25" s="15" t="n">
         <f aca="false">IF(L25="","",H25/L25-1)</f>
-        <v>0.0943624575292503</v>
+        <v>0.0988704887067038</v>
       </c>
       <c r="O25" s="15" t="str">
-        <f aca="false">IF(AND(F25="Accumulate",N25&lt;&gt;"",N25&gt;0),MIN(Policy!$B$4/N25,IF(E25="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F25="Accumulate",N25&lt;&gt;"",N25&gt;0),MIN(Policy!$B$4/(N25+Policy!$B$12),IF(E25="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P25" s="16" t="str">
@@ -3798,16 +3770,16 @@
         <v>152</v>
       </c>
       <c r="C26" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D26" s="10" t="s">
         <v>153</v>
       </c>
       <c r="E26" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F26" s="19" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="G26" s="12" t="s">
         <v>134</v>
@@ -3822,19 +3794,19 @@
         <v>46.77</v>
       </c>
       <c r="K26" s="13" t="n">
-        <v>46.3637073170732</v>
+        <v>46.31655</v>
       </c>
       <c r="L26" s="14" t="n">
         <f aca="false">IF(K26="","",K26*(1-Policy!$B$7))</f>
-        <v>44.972796097561</v>
+        <v>44.9270535</v>
       </c>
       <c r="M26" s="14"/>
       <c r="N26" s="15" t="n">
         <f aca="false">IF(L26="","",H26/L26-1)</f>
-        <v>0.0399620227868485</v>
+        <v>0.0410208628527133</v>
       </c>
       <c r="O26" s="15" t="str">
-        <f aca="false">IF(AND(F26="Accumulate",N26&lt;&gt;"",N26&gt;0),MIN(Policy!$B$4/N26,IF(E26="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F26="Accumulate",N26&lt;&gt;"",N26&gt;0),MIN(Policy!$B$4/(N26+Policy!$B$12),IF(E26="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P26" s="16" t="str">
@@ -3865,7 +3837,7 @@
         <v>133</v>
       </c>
       <c r="E27" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F27" s="20" t="s">
         <v>157</v>
@@ -3891,7 +3863,7 @@
         <v/>
       </c>
       <c r="O27" s="15" t="str">
-        <f aca="false">IF(AND(F27="Accumulate",N27&lt;&gt;"",N27&gt;0),MIN(Policy!$B$4/N27,IF(E27="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F27="Accumulate",N27&lt;&gt;"",N27&gt;0),MIN(Policy!$B$4/(N27+Policy!$B$12),IF(E27="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P27" s="16" t="str">
@@ -3922,7 +3894,7 @@
         <v>133</v>
       </c>
       <c r="E28" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F28" s="20" t="s">
         <v>157</v>
@@ -3948,7 +3920,7 @@
         <v/>
       </c>
       <c r="O28" s="15" t="str">
-        <f aca="false">IF(AND(F28="Accumulate",N28&lt;&gt;"",N28&gt;0),MIN(Policy!$B$4/N28,IF(E28="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F28="Accumulate",N28&lt;&gt;"",N28&gt;0),MIN(Policy!$B$4/(N28+Policy!$B$12),IF(E28="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P28" s="16" t="str">
@@ -3976,10 +3948,10 @@
         <v>156</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E29" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F29" s="20" t="s">
         <v>157</v>
@@ -4005,7 +3977,7 @@
         <v/>
       </c>
       <c r="O29" s="15" t="str">
-        <f aca="false">IF(AND(F29="Accumulate",N29&lt;&gt;"",N29&gt;0),MIN(Policy!$B$4/N29,IF(E29="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F29="Accumulate",N29&lt;&gt;"",N29&gt;0),MIN(Policy!$B$4/(N29+Policy!$B$12),IF(E29="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P29" s="16" t="str">
@@ -4030,13 +4002,13 @@
         <v>164</v>
       </c>
       <c r="C30" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D30" s="10" t="s">
         <v>165</v>
       </c>
       <c r="E30" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F30" s="20" t="s">
         <v>157</v>
@@ -4062,7 +4034,7 @@
         <v/>
       </c>
       <c r="O30" s="15" t="str">
-        <f aca="false">IF(AND(F30="Accumulate",N30&lt;&gt;"",N30&gt;0),MIN(Policy!$B$4/N30,IF(E30="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F30="Accumulate",N30&lt;&gt;"",N30&gt;0),MIN(Policy!$B$4/(N30+Policy!$B$12),IF(E30="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P30" s="16" t="str">
@@ -4087,13 +4059,13 @@
         <v>167</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D31" s="10" t="s">
         <v>133</v>
       </c>
       <c r="E31" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F31" s="20" t="s">
         <v>157</v>
@@ -4119,7 +4091,7 @@
         <v/>
       </c>
       <c r="O31" s="15" t="str">
-        <f aca="false">IF(AND(F31="Accumulate",N31&lt;&gt;"",N31&gt;0),MIN(Policy!$B$4/N31,IF(E31="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F31="Accumulate",N31&lt;&gt;"",N31&gt;0),MIN(Policy!$B$4/(N31+Policy!$B$12),IF(E31="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P31" s="16" t="str">
@@ -4147,10 +4119,10 @@
         <v>170</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E32" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F32" s="20" t="s">
         <v>157</v>
@@ -4169,14 +4141,14 @@
         <v/>
       </c>
       <c r="M32" s="14" t="n">
-        <v>9.90134146341463</v>
+        <v>9.935875</v>
       </c>
       <c r="N32" s="15" t="str">
         <f aca="false">IF(L32="","",H32/L32-1)</f>
         <v/>
       </c>
       <c r="O32" s="15" t="str">
-        <f aca="false">IF(AND(F32="Accumulate",N32&lt;&gt;"",N32&gt;0),MIN(Policy!$B$4/N32,IF(E32="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F32="Accumulate",N32&lt;&gt;"",N32&gt;0),MIN(Policy!$B$4/(N32+Policy!$B$12),IF(E32="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P32" s="16" t="str">
@@ -4207,7 +4179,7 @@
         <v>133</v>
       </c>
       <c r="E33" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F33" s="20" t="s">
         <v>157</v>
@@ -4233,7 +4205,7 @@
         <v/>
       </c>
       <c r="O33" s="15" t="str">
-        <f aca="false">IF(AND(F33="Accumulate",N33&lt;&gt;"",N33&gt;0),MIN(Policy!$B$4/N33,IF(E33="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F33="Accumulate",N33&lt;&gt;"",N33&gt;0),MIN(Policy!$B$4/(N33+Policy!$B$12),IF(E33="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P33" s="16" t="str">
@@ -4258,13 +4230,13 @@
         <v>173</v>
       </c>
       <c r="C34" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D34" s="10" t="s">
         <v>143</v>
       </c>
       <c r="E34" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F34" s="20" t="s">
         <v>157</v>
@@ -4283,14 +4255,14 @@
         <v/>
       </c>
       <c r="M34" s="14" t="n">
-        <v>24.6663414634146</v>
+        <v>24.7265</v>
       </c>
       <c r="N34" s="15" t="str">
         <f aca="false">IF(L34="","",H34/L34-1)</f>
         <v/>
       </c>
       <c r="O34" s="15" t="str">
-        <f aca="false">IF(AND(F34="Accumulate",N34&lt;&gt;"",N34&gt;0),MIN(Policy!$B$4/N34,IF(E34="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F34="Accumulate",N34&lt;&gt;"",N34&gt;0),MIN(Policy!$B$4/(N34+Policy!$B$12),IF(E34="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P34" s="16" t="str">
@@ -4321,7 +4293,7 @@
         <v>176</v>
       </c>
       <c r="E35" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F35" s="20" t="s">
         <v>157</v>
@@ -4347,7 +4319,7 @@
         <v/>
       </c>
       <c r="O35" s="15" t="str">
-        <f aca="false">IF(AND(F35="Accumulate",N35&lt;&gt;"",N35&gt;0),MIN(Policy!$B$4/N35,IF(E35="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F35="Accumulate",N35&lt;&gt;"",N35&gt;0),MIN(Policy!$B$4/(N35+Policy!$B$12),IF(E35="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P35" s="16" t="str">
@@ -4372,13 +4344,13 @@
         <v>178</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D36" s="10" t="s">
         <v>179</v>
       </c>
       <c r="E36" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F36" s="20" t="s">
         <v>157</v>
@@ -4404,7 +4376,7 @@
         <v/>
       </c>
       <c r="O36" s="15" t="str">
-        <f aca="false">IF(AND(F36="Accumulate",N36&lt;&gt;"",N36&gt;0),MIN(Policy!$B$4/N36,IF(E36="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F36="Accumulate",N36&lt;&gt;"",N36&gt;0),MIN(Policy!$B$4/(N36+Policy!$B$12),IF(E36="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P36" s="16" t="str">
@@ -4429,13 +4401,13 @@
         <v>181</v>
       </c>
       <c r="C37" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E37" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F37" s="20" t="s">
         <v>157</v>
@@ -4461,7 +4433,7 @@
         <v/>
       </c>
       <c r="O37" s="15" t="str">
-        <f aca="false">IF(AND(F37="Accumulate",N37&lt;&gt;"",N37&gt;0),MIN(Policy!$B$4/N37,IF(E37="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F37="Accumulate",N37&lt;&gt;"",N37&gt;0),MIN(Policy!$B$4/(N37+Policy!$B$12),IF(E37="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P37" s="16" t="str">
@@ -4492,7 +4464,7 @@
         <v>176</v>
       </c>
       <c r="E38" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F38" s="20" t="s">
         <v>157</v>
@@ -4518,7 +4490,7 @@
         <v/>
       </c>
       <c r="O38" s="15" t="str">
-        <f aca="false">IF(AND(F38="Accumulate",N38&lt;&gt;"",N38&gt;0),MIN(Policy!$B$4/N38,IF(E38="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F38="Accumulate",N38&lt;&gt;"",N38&gt;0),MIN(Policy!$B$4/(N38+Policy!$B$12),IF(E38="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P38" s="16" t="str">
@@ -4543,13 +4515,13 @@
         <v>185</v>
       </c>
       <c r="C39" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D39" s="10" t="s">
         <v>165</v>
       </c>
       <c r="E39" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F39" s="20" t="s">
         <v>157</v>
@@ -4575,7 +4547,7 @@
         <v/>
       </c>
       <c r="O39" s="15" t="str">
-        <f aca="false">IF(AND(F39="Accumulate",N39&lt;&gt;"",N39&gt;0),MIN(Policy!$B$4/N39,IF(E39="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F39="Accumulate",N39&lt;&gt;"",N39&gt;0),MIN(Policy!$B$4/(N39+Policy!$B$12),IF(E39="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P39" s="16" t="str">
@@ -4600,13 +4572,13 @@
         <v>187</v>
       </c>
       <c r="C40" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D40" s="10" t="s">
         <v>188</v>
       </c>
       <c r="E40" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F40" s="20" t="s">
         <v>157</v>
@@ -4632,7 +4604,7 @@
         <v/>
       </c>
       <c r="O40" s="15" t="str">
-        <f aca="false">IF(AND(F40="Accumulate",N40&lt;&gt;"",N40&gt;0),MIN(Policy!$B$4/N40,IF(E40="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F40="Accumulate",N40&lt;&gt;"",N40&gt;0),MIN(Policy!$B$4/(N40+Policy!$B$12),IF(E40="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P40" s="16" t="str">
@@ -4657,13 +4629,13 @@
         <v>190</v>
       </c>
       <c r="C41" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D41" s="10" t="s">
         <v>133</v>
       </c>
       <c r="E41" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F41" s="20" t="s">
         <v>157</v>
@@ -4689,7 +4661,7 @@
         <v/>
       </c>
       <c r="O41" s="15" t="str">
-        <f aca="false">IF(AND(F41="Accumulate",N41&lt;&gt;"",N41&gt;0),MIN(Policy!$B$4/N41,IF(E41="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F41="Accumulate",N41&lt;&gt;"",N41&gt;0),MIN(Policy!$B$4/(N41+Policy!$B$12),IF(E41="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P41" s="16" t="str">
@@ -4714,13 +4686,13 @@
         <v>192</v>
       </c>
       <c r="C42" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D42" s="10" t="s">
         <v>133</v>
       </c>
       <c r="E42" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F42" s="20" t="s">
         <v>157</v>
@@ -4746,7 +4718,7 @@
         <v/>
       </c>
       <c r="O42" s="15" t="str">
-        <f aca="false">IF(AND(F42="Accumulate",N42&lt;&gt;"",N42&gt;0),MIN(Policy!$B$4/N42,IF(E42="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F42="Accumulate",N42&lt;&gt;"",N42&gt;0),MIN(Policy!$B$4/(N42+Policy!$B$12),IF(E42="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P42" s="16" t="str">
@@ -4771,13 +4743,13 @@
         <v>194</v>
       </c>
       <c r="C43" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D43" s="10" t="s">
         <v>176</v>
       </c>
       <c r="E43" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F43" s="20" t="s">
         <v>157</v>
@@ -4803,7 +4775,7 @@
         <v/>
       </c>
       <c r="O43" s="15" t="str">
-        <f aca="false">IF(AND(F43="Accumulate",N43&lt;&gt;"",N43&gt;0),MIN(Policy!$B$4/N43,IF(E43="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F43="Accumulate",N43&lt;&gt;"",N43&gt;0),MIN(Policy!$B$4/(N43+Policy!$B$12),IF(E43="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P43" s="16" t="str">
@@ -4828,13 +4800,13 @@
         <v>196</v>
       </c>
       <c r="C44" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D44" s="10" t="s">
         <v>197</v>
       </c>
       <c r="E44" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F44" s="20" t="s">
         <v>157</v>
@@ -4860,7 +4832,7 @@
         <v/>
       </c>
       <c r="O44" s="15" t="str">
-        <f aca="false">IF(AND(F44="Accumulate",N44&lt;&gt;"",N44&gt;0),MIN(Policy!$B$4/N44,IF(E44="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F44="Accumulate",N44&lt;&gt;"",N44&gt;0),MIN(Policy!$B$4/(N44+Policy!$B$12),IF(E44="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P44" s="16" t="str">
@@ -4891,7 +4863,7 @@
         <v>133</v>
       </c>
       <c r="E45" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F45" s="20" t="s">
         <v>157</v>
@@ -4917,7 +4889,7 @@
         <v/>
       </c>
       <c r="O45" s="15" t="str">
-        <f aca="false">IF(AND(F45="Accumulate",N45&lt;&gt;"",N45&gt;0),MIN(Policy!$B$4/N45,IF(E45="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F45="Accumulate",N45&lt;&gt;"",N45&gt;0),MIN(Policy!$B$4/(N45+Policy!$B$12),IF(E45="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P45" s="16" t="str">
@@ -4942,13 +4914,13 @@
         <v>201</v>
       </c>
       <c r="C46" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="E46" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F46" s="20" t="s">
         <v>157</v>
@@ -4974,7 +4946,7 @@
         <v/>
       </c>
       <c r="O46" s="15" t="str">
-        <f aca="false">IF(AND(F46="Accumulate",N46&lt;&gt;"",N46&gt;0),MIN(Policy!$B$4/N46,IF(E46="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F46="Accumulate",N46&lt;&gt;"",N46&gt;0),MIN(Policy!$B$4/(N46+Policy!$B$12),IF(E46="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P46" s="16" t="str">
@@ -4999,13 +4971,13 @@
         <v>203</v>
       </c>
       <c r="C47" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D47" s="10" t="s">
         <v>133</v>
       </c>
       <c r="E47" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F47" s="20" t="s">
         <v>157</v>
@@ -5031,7 +5003,7 @@
         <v/>
       </c>
       <c r="O47" s="15" t="str">
-        <f aca="false">IF(AND(F47="Accumulate",N47&lt;&gt;"",N47&gt;0),MIN(Policy!$B$4/N47,IF(E47="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F47="Accumulate",N47&lt;&gt;"",N47&gt;0),MIN(Policy!$B$4/(N47+Policy!$B$12),IF(E47="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P47" s="16" t="str">
@@ -5056,13 +5028,13 @@
         <v>205</v>
       </c>
       <c r="C48" s="10" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="D48" s="10" t="s">
         <v>206</v>
       </c>
       <c r="E48" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F48" s="20" t="s">
         <v>157</v>
@@ -5081,14 +5053,14 @@
         <v/>
       </c>
       <c r="M48" s="14" t="n">
-        <v>11.3504878048781</v>
+        <v>11.33275</v>
       </c>
       <c r="N48" s="15" t="str">
         <f aca="false">IF(L48="","",H48/L48-1)</f>
         <v/>
       </c>
       <c r="O48" s="15" t="str">
-        <f aca="false">IF(AND(F48="Accumulate",N48&lt;&gt;"",N48&gt;0),MIN(Policy!$B$4/N48,IF(E48="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F48="Accumulate",N48&lt;&gt;"",N48&gt;0),MIN(Policy!$B$4/(N48+Policy!$B$12),IF(E48="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P48" s="16" t="str">
@@ -5113,13 +5085,13 @@
         <v>208</v>
       </c>
       <c r="C49" s="10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D49" s="10" t="s">
         <v>209</v>
       </c>
       <c r="E49" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F49" s="20" t="s">
         <v>157</v>
@@ -5138,14 +5110,14 @@
         <v/>
       </c>
       <c r="M49" s="14" t="n">
-        <v>87.2585365853659</v>
+        <v>87.236</v>
       </c>
       <c r="N49" s="15" t="str">
         <f aca="false">IF(L49="","",H49/L49-1)</f>
         <v/>
       </c>
       <c r="O49" s="15" t="str">
-        <f aca="false">IF(AND(F49="Accumulate",N49&lt;&gt;"",N49&gt;0),MIN(Policy!$B$4/N49,IF(E49="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F49="Accumulate",N49&lt;&gt;"",N49&gt;0),MIN(Policy!$B$4/(N49+Policy!$B$12),IF(E49="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P49" s="16" t="str">
@@ -5170,13 +5142,13 @@
         <v>211</v>
       </c>
       <c r="C50" s="10" t="s">
-        <v>79</v>
+        <v>170</v>
       </c>
       <c r="D50" s="10" t="s">
         <v>212</v>
       </c>
       <c r="E50" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F50" s="20" t="s">
         <v>157</v>
@@ -5185,7 +5157,7 @@
         <v>158</v>
       </c>
       <c r="H50" s="13" t="n">
-        <v>18.574</v>
+        <v>37.32</v>
       </c>
       <c r="I50" s="13"/>
       <c r="J50" s="13"/>
@@ -5195,14 +5167,14 @@
         <v/>
       </c>
       <c r="M50" s="14" t="n">
-        <v>20.2704</v>
+        <v>38.088</v>
       </c>
       <c r="N50" s="15" t="str">
         <f aca="false">IF(L50="","",H50/L50-1)</f>
         <v/>
       </c>
       <c r="O50" s="15" t="str">
-        <f aca="false">IF(AND(F50="Accumulate",N50&lt;&gt;"",N50&gt;0),MIN(Policy!$B$4/N50,IF(E50="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F50="Accumulate",N50&lt;&gt;"",N50&gt;0),MIN(Policy!$B$4/(N50+Policy!$B$12),IF(E50="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P50" s="16" t="str">
@@ -5210,13 +5182,13 @@
         <v/>
       </c>
       <c r="Q50" s="17" t="n">
-        <v>0.00345759049162608</v>
+        <v>-0.00320512820512808</v>
       </c>
       <c r="R50" s="17" t="n">
-        <v>-0.0656941649899395</v>
+        <v>-0.0866372980910426</v>
       </c>
       <c r="S50" s="18" t="n">
-        <v>-0.0793167183981112</v>
+        <v>-0.18924845217083</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5227,13 +5199,13 @@
         <v>214</v>
       </c>
       <c r="C51" s="10" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>215</v>
+        <v>106</v>
       </c>
       <c r="E51" s="10" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F51" s="20" t="s">
         <v>157</v>
@@ -5242,7 +5214,7 @@
         <v>158</v>
       </c>
       <c r="H51" s="13" t="n">
-        <v>41.61</v>
+        <v>120.24</v>
       </c>
       <c r="I51" s="13"/>
       <c r="J51" s="13"/>
@@ -5252,14 +5224,14 @@
         <v/>
       </c>
       <c r="M51" s="14" t="n">
-        <v>43.367</v>
+        <v>135.0835</v>
       </c>
       <c r="N51" s="15" t="str">
         <f aca="false">IF(L51="","",H51/L51-1)</f>
         <v/>
       </c>
       <c r="O51" s="15" t="str">
-        <f aca="false">IF(AND(F51="Accumulate",N51&lt;&gt;"",N51&gt;0),MIN(Policy!$B$4/N51,IF(E51="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F51="Accumulate",N51&lt;&gt;"",N51&gt;0),MIN(Policy!$B$4/(N51+Policy!$B$12),IF(E51="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P51" s="16" t="str">
@@ -5267,30 +5239,30 @@
         <v/>
       </c>
       <c r="Q51" s="17" t="n">
-        <v>-0.0638920134983128</v>
+        <v>-0.0687732342007436</v>
       </c>
       <c r="R51" s="17" t="n">
-        <v>0.0228613569321534</v>
+        <v>-0.0576802507836991</v>
       </c>
       <c r="S51" s="18" t="n">
-        <v>-0.136293334939637</v>
+        <v>-0.234010297001579</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="B52" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="B52" s="10" t="s">
+      <c r="C52" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="D52" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="C52" s="10" t="s">
-        <v>170</v>
-      </c>
-      <c r="D52" s="10" t="s">
-        <v>215</v>
-      </c>
       <c r="E52" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F52" s="20" t="s">
         <v>157</v>
@@ -5299,7 +5271,7 @@
         <v>158</v>
       </c>
       <c r="H52" s="13" t="n">
-        <v>37.32</v>
+        <v>3.98</v>
       </c>
       <c r="I52" s="13"/>
       <c r="J52" s="13"/>
@@ -5309,14 +5281,14 @@
         <v/>
       </c>
       <c r="M52" s="14" t="n">
-        <v>38.088</v>
+        <v>4.074</v>
       </c>
       <c r="N52" s="15" t="str">
         <f aca="false">IF(L52="","",H52/L52-1)</f>
         <v/>
       </c>
       <c r="O52" s="15" t="str">
-        <f aca="false">IF(AND(F52="Accumulate",N52&lt;&gt;"",N52&gt;0),MIN(Policy!$B$4/N52,IF(E52="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F52="Accumulate",N52&lt;&gt;"",N52&gt;0),MIN(Policy!$B$4/(N52+Policy!$B$12),IF(E52="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P52" s="16" t="str">
@@ -5324,16 +5296,16 @@
         <v/>
       </c>
       <c r="Q52" s="17" t="n">
-        <v>-0.00320512820512808</v>
+        <v>-0.0316301703163018</v>
       </c>
       <c r="R52" s="17" t="n">
-        <v>-0.0866372980910426</v>
+        <v>-0.038647342995169</v>
       </c>
       <c r="S52" s="18" t="n">
-        <v>-0.18924845217083</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>-0.436560488438466</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="10" t="s">
         <v>218</v>
       </c>
@@ -5341,22 +5313,22 @@
         <v>219</v>
       </c>
       <c r="C53" s="10" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="E53" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F53" s="20" t="s">
-        <v>157</v>
+        <v>76</v>
+      </c>
+      <c r="F53" s="21" t="s">
+        <v>220</v>
       </c>
       <c r="G53" s="12" t="s">
-        <v>158</v>
+        <v>221</v>
       </c>
       <c r="H53" s="13" t="n">
-        <v>120.24</v>
+        <v>83.43</v>
       </c>
       <c r="I53" s="13"/>
       <c r="J53" s="13"/>
@@ -5366,14 +5338,14 @@
         <v/>
       </c>
       <c r="M53" s="14" t="n">
-        <v>135.113170731707</v>
+        <v>84.18875</v>
       </c>
       <c r="N53" s="15" t="str">
         <f aca="false">IF(L53="","",H53/L53-1)</f>
         <v/>
       </c>
       <c r="O53" s="15" t="str">
-        <f aca="false">IF(AND(F53="Accumulate",N53&lt;&gt;"",N53&gt;0),MIN(Policy!$B$4/N53,IF(E53="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F53="Accumulate",N53&lt;&gt;"",N53&gt;0),MIN(Policy!$B$4/(N53+Policy!$B$12),IF(E53="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P53" s="16" t="str">
@@ -5381,39 +5353,39 @@
         <v/>
       </c>
       <c r="Q53" s="17" t="n">
-        <v>-0.0687732342007436</v>
+        <v>-0.00820256776034234</v>
       </c>
       <c r="R53" s="17" t="n">
-        <v>-0.0576802507836991</v>
+        <v>0.068245838668374</v>
       </c>
       <c r="S53" s="18" t="n">
-        <v>-0.234010297001579</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0.220779801431815</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="B54" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D54" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="E54" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="F54" s="21" t="s">
         <v>220</v>
       </c>
-      <c r="B54" s="10" t="s">
+      <c r="G54" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="C54" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>222</v>
-      </c>
-      <c r="E54" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="F54" s="20" t="s">
-        <v>157</v>
-      </c>
-      <c r="G54" s="12" t="s">
-        <v>158</v>
-      </c>
       <c r="H54" s="13" t="n">
-        <v>3.98</v>
+        <v>54.78</v>
       </c>
       <c r="I54" s="13"/>
       <c r="J54" s="13"/>
@@ -5423,14 +5395,14 @@
         <v/>
       </c>
       <c r="M54" s="14" t="n">
-        <v>4.074</v>
+        <v>65.1445</v>
       </c>
       <c r="N54" s="15" t="str">
         <f aca="false">IF(L54="","",H54/L54-1)</f>
         <v/>
       </c>
       <c r="O54" s="15" t="str">
-        <f aca="false">IF(AND(F54="Accumulate",N54&lt;&gt;"",N54&gt;0),MIN(Policy!$B$4/N54,IF(E54="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F54="Accumulate",N54&lt;&gt;"",N54&gt;0),MIN(Policy!$B$4/(N54+Policy!$B$12),IF(E54="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P54" s="16" t="str">
@@ -5438,39 +5410,39 @@
         <v/>
       </c>
       <c r="Q54" s="17" t="n">
-        <v>-0.0316301703163018</v>
+        <v>0.0153846153846153</v>
       </c>
       <c r="R54" s="17" t="n">
-        <v>-0.038647342995169</v>
+        <v>0.205811138014528</v>
       </c>
       <c r="S54" s="18" t="n">
-        <v>-0.436560488438466</v>
+        <v>0.20654356179894</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B55" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C55" s="10" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>153</v>
+        <v>227</v>
       </c>
       <c r="E55" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F55" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G55" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H55" s="13" t="n">
-        <v>83.43</v>
+        <v>384.58</v>
       </c>
       <c r="I55" s="13"/>
       <c r="J55" s="13"/>
@@ -5480,14 +5452,14 @@
         <v/>
       </c>
       <c r="M55" s="14" t="n">
-        <v>84.030243902439</v>
+        <v>415.75125</v>
       </c>
       <c r="N55" s="15" t="str">
         <f aca="false">IF(L55="","",H55/L55-1)</f>
         <v/>
       </c>
       <c r="O55" s="15" t="str">
-        <f aca="false">IF(AND(F55="Accumulate",N55&lt;&gt;"",N55&gt;0),MIN(Policy!$B$4/N55,IF(E55="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F55="Accumulate",N55&lt;&gt;"",N55&gt;0),MIN(Policy!$B$4/(N55+Policy!$B$12),IF(E55="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P55" s="16" t="str">
@@ -5495,39 +5467,39 @@
         <v/>
       </c>
       <c r="Q55" s="17" t="n">
-        <v>-0.00820256776034234</v>
+        <v>0.020079042996207</v>
       </c>
       <c r="R55" s="17" t="n">
-        <v>0.068245838668374</v>
+        <v>0.0418833983528391</v>
       </c>
       <c r="S55" s="18" t="n">
-        <v>0.220779801431815</v>
+        <v>0.128584143934243</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="10" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B56" s="10" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C56" s="10" t="s">
-        <v>85</v>
+        <v>132</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E56" s="10" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F56" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G56" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H56" s="13" t="n">
-        <v>54.78</v>
+        <v>52.83</v>
       </c>
       <c r="I56" s="13"/>
       <c r="J56" s="13"/>
@@ -5537,14 +5509,14 @@
         <v/>
       </c>
       <c r="M56" s="14" t="n">
-        <v>65.1592682926829</v>
+        <v>57.16275</v>
       </c>
       <c r="N56" s="15" t="str">
         <f aca="false">IF(L56="","",H56/L56-1)</f>
         <v/>
       </c>
       <c r="O56" s="15" t="str">
-        <f aca="false">IF(AND(F56="Accumulate",N56&lt;&gt;"",N56&gt;0),MIN(Policy!$B$4/N56,IF(E56="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F56="Accumulate",N56&lt;&gt;"",N56&gt;0),MIN(Policy!$B$4/(N56+Policy!$B$12),IF(E56="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P56" s="16" t="str">
@@ -5552,39 +5524,39 @@
         <v/>
       </c>
       <c r="Q56" s="17" t="n">
-        <v>0.0153846153846153</v>
+        <v>0.0677041228779305</v>
       </c>
       <c r="R56" s="17" t="n">
-        <v>0.205811138014528</v>
+        <v>-0.0487936622254231</v>
       </c>
       <c r="S56" s="18" t="n">
-        <v>0.20654356179894</v>
+        <v>0.0374850053310838</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="10" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B57" s="10" t="s">
         <v>231</v>
       </c>
       <c r="C57" s="10" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>232</v>
+        <v>106</v>
       </c>
       <c r="E57" s="10" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F57" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H57" s="13" t="n">
-        <v>384.58</v>
+        <v>17.544</v>
       </c>
       <c r="I57" s="13"/>
       <c r="J57" s="13"/>
@@ -5594,14 +5566,14 @@
         <v/>
       </c>
       <c r="M57" s="14" t="n">
-        <v>415.32512195122</v>
+        <v>19.51085</v>
       </c>
       <c r="N57" s="15" t="str">
         <f aca="false">IF(L57="","",H57/L57-1)</f>
         <v/>
       </c>
       <c r="O57" s="15" t="str">
-        <f aca="false">IF(AND(F57="Accumulate",N57&lt;&gt;"",N57&gt;0),MIN(Policy!$B$4/N57,IF(E57="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F57="Accumulate",N57&lt;&gt;"",N57&gt;0),MIN(Policy!$B$4/(N57+Policy!$B$12),IF(E57="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P57" s="16" t="str">
@@ -5609,39 +5581,39 @@
         <v/>
       </c>
       <c r="Q57" s="17" t="n">
-        <v>0.020079042996207</v>
+        <v>-0.104623864448301</v>
       </c>
       <c r="R57" s="17" t="n">
-        <v>0.0418833983528391</v>
+        <v>0.0793650793650793</v>
       </c>
       <c r="S57" s="18" t="n">
-        <v>0.128584143934243</v>
+        <v>-0.0425352054570563</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="B58" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="B58" s="10" t="s">
-        <v>234</v>
-      </c>
       <c r="C58" s="10" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>235</v>
+        <v>143</v>
       </c>
       <c r="E58" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F58" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H58" s="13" t="n">
-        <v>52.83</v>
+        <v>11.48</v>
       </c>
       <c r="I58" s="13"/>
       <c r="J58" s="13"/>
@@ -5651,14 +5623,14 @@
         <v/>
       </c>
       <c r="M58" s="14" t="n">
-        <v>57.5041463414634</v>
+        <v>12.3777</v>
       </c>
       <c r="N58" s="15" t="str">
         <f aca="false">IF(L58="","",H58/L58-1)</f>
         <v/>
       </c>
       <c r="O58" s="15" t="str">
-        <f aca="false">IF(AND(F58="Accumulate",N58&lt;&gt;"",N58&gt;0),MIN(Policy!$B$4/N58,IF(E58="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F58="Accumulate",N58&lt;&gt;"",N58&gt;0),MIN(Policy!$B$4/(N58+Policy!$B$12),IF(E58="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P58" s="16" t="str">
@@ -5666,39 +5638,39 @@
         <v/>
       </c>
       <c r="Q58" s="17" t="n">
-        <v>0.0677041228779305</v>
+        <v>-0.065907241659886</v>
       </c>
       <c r="R58" s="17" t="n">
-        <v>-0.0487936622254231</v>
+        <v>0.0394784498370155</v>
       </c>
       <c r="S58" s="18" t="n">
-        <v>0.0374850053310838</v>
+        <v>-0.0562098348034994</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="B59" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D59" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="B59" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>101</v>
-      </c>
       <c r="E59" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F59" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H59" s="13" t="n">
-        <v>17.544</v>
+        <v>18.574</v>
       </c>
       <c r="I59" s="13"/>
       <c r="J59" s="13"/>
@@ -5708,14 +5680,14 @@
         <v/>
       </c>
       <c r="M59" s="14" t="n">
-        <v>19.4807317073171</v>
+        <v>20.3037</v>
       </c>
       <c r="N59" s="15" t="str">
         <f aca="false">IF(L59="","",H59/L59-1)</f>
         <v/>
       </c>
       <c r="O59" s="15" t="str">
-        <f aca="false">IF(AND(F59="Accumulate",N59&lt;&gt;"",N59&gt;0),MIN(Policy!$B$4/N59,IF(E59="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F59="Accumulate",N59&lt;&gt;"",N59&gt;0),MIN(Policy!$B$4/(N59+Policy!$B$12),IF(E59="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P59" s="16" t="str">
@@ -5723,13 +5695,13 @@
         <v/>
       </c>
       <c r="Q59" s="17" t="n">
-        <v>-0.104623864448301</v>
+        <v>0.00345759049162608</v>
       </c>
       <c r="R59" s="17" t="n">
-        <v>0.0793650793650793</v>
+        <v>-0.0656941649899395</v>
       </c>
       <c r="S59" s="18" t="n">
-        <v>-0.0425352054570563</v>
+        <v>-0.0793167183981112</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5740,22 +5712,22 @@
         <v>238</v>
       </c>
       <c r="C60" s="10" t="s">
-        <v>79</v>
+        <v>170</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>143</v>
+        <v>230</v>
       </c>
       <c r="E60" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F60" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H60" s="13" t="n">
-        <v>11.48</v>
+        <v>71.26</v>
       </c>
       <c r="I60" s="13"/>
       <c r="J60" s="13"/>
@@ -5765,14 +5737,14 @@
         <v/>
       </c>
       <c r="M60" s="14" t="n">
-        <v>12.357512195122</v>
+        <v>79.798</v>
       </c>
       <c r="N60" s="15" t="str">
         <f aca="false">IF(L60="","",H60/L60-1)</f>
         <v/>
       </c>
       <c r="O60" s="15" t="str">
-        <f aca="false">IF(AND(F60="Accumulate",N60&lt;&gt;"",N60&gt;0),MIN(Policy!$B$4/N60,IF(E60="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F60="Accumulate",N60&lt;&gt;"",N60&gt;0),MIN(Policy!$B$4/(N60+Policy!$B$12),IF(E60="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P60" s="16" t="str">
@@ -5780,13 +5752,13 @@
         <v/>
       </c>
       <c r="Q60" s="17" t="n">
-        <v>-0.065907241659886</v>
+        <v>-0.0192678227360307</v>
       </c>
       <c r="R60" s="17" t="n">
-        <v>0.0394784498370155</v>
+        <v>-0.035723951285521</v>
       </c>
       <c r="S60" s="18" t="n">
-        <v>-0.0562098348034994</v>
+        <v>-0.0881131747598993</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5797,22 +5769,22 @@
         <v>240</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>170</v>
+        <v>156</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E61" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F61" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H61" s="13" t="n">
-        <v>71.26</v>
+        <v>4.24</v>
       </c>
       <c r="I61" s="13"/>
       <c r="J61" s="13"/>
@@ -5822,14 +5794,14 @@
         <v/>
       </c>
       <c r="M61" s="14" t="n">
-        <v>79.8834146341464</v>
+        <v>4.587</v>
       </c>
       <c r="N61" s="15" t="str">
         <f aca="false">IF(L61="","",H61/L61-1)</f>
         <v/>
       </c>
       <c r="O61" s="15" t="str">
-        <f aca="false">IF(AND(F61="Accumulate",N61&lt;&gt;"",N61&gt;0),MIN(Policy!$B$4/N61,IF(E61="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F61="Accumulate",N61&lt;&gt;"",N61&gt;0),MIN(Policy!$B$4/(N61+Policy!$B$12),IF(E61="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P61" s="16" t="str">
@@ -5837,39 +5809,39 @@
         <v/>
       </c>
       <c r="Q61" s="17" t="n">
-        <v>-0.0192678227360307</v>
+        <v>-0.0363636363636364</v>
       </c>
       <c r="R61" s="17" t="n">
-        <v>-0.035723951285521</v>
+        <v>-0.00469483568075102</v>
       </c>
       <c r="S61" s="18" t="n">
-        <v>-0.0881131747598993</v>
+        <v>-0.103914078846694</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B62" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C62" s="10" t="s">
-        <v>156</v>
+        <v>74</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>243</v>
+        <v>109</v>
       </c>
       <c r="E62" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F62" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G62" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H62" s="13" t="n">
-        <v>4.24</v>
+        <v>110.38</v>
       </c>
       <c r="I62" s="13"/>
       <c r="J62" s="13"/>
@@ -5879,14 +5851,14 @@
         <v/>
       </c>
       <c r="M62" s="14" t="n">
-        <v>4.58682926829268</v>
+        <v>113.2685</v>
       </c>
       <c r="N62" s="15" t="str">
         <f aca="false">IF(L62="","",H62/L62-1)</f>
         <v/>
       </c>
       <c r="O62" s="15" t="str">
-        <f aca="false">IF(AND(F62="Accumulate",N62&lt;&gt;"",N62&gt;0),MIN(Policy!$B$4/N62,IF(E62="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F62="Accumulate",N62&lt;&gt;"",N62&gt;0),MIN(Policy!$B$4/(N62+Policy!$B$12),IF(E62="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P62" s="16" t="str">
@@ -5894,13 +5866,13 @@
         <v/>
       </c>
       <c r="Q62" s="17" t="n">
-        <v>-0.0363636363636364</v>
+        <v>-0.011286277319957</v>
       </c>
       <c r="R62" s="17" t="n">
-        <v>-0.00469483568075102</v>
+        <v>-0.0214539007092198</v>
       </c>
       <c r="S62" s="18" t="n">
-        <v>-0.103914078846694</v>
+        <v>-0.106660502592929</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5911,22 +5883,22 @@
         <v>245</v>
       </c>
       <c r="C63" s="10" t="s">
-        <v>72</v>
+        <v>156</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>104</v>
+        <v>246</v>
       </c>
       <c r="E63" s="10" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="F63" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G63" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H63" s="13" t="n">
-        <v>110.38</v>
+        <v>0.955</v>
       </c>
       <c r="I63" s="13"/>
       <c r="J63" s="13"/>
@@ -5936,14 +5908,14 @@
         <v/>
       </c>
       <c r="M63" s="14" t="n">
-        <v>113.357073170732</v>
+        <v>0.98275</v>
       </c>
       <c r="N63" s="15" t="str">
         <f aca="false">IF(L63="","",H63/L63-1)</f>
         <v/>
       </c>
       <c r="O63" s="15" t="str">
-        <f aca="false">IF(AND(F63="Accumulate",N63&lt;&gt;"",N63&gt;0),MIN(Policy!$B$4/N63,IF(E63="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F63="Accumulate",N63&lt;&gt;"",N63&gt;0),MIN(Policy!$B$4/(N63+Policy!$B$12),IF(E63="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P63" s="16" t="str">
@@ -5951,39 +5923,39 @@
         <v/>
       </c>
       <c r="Q63" s="17" t="n">
-        <v>-0.011286277319957</v>
+        <v>-0.0154639175257733</v>
       </c>
       <c r="R63" s="17" t="n">
-        <v>-0.0214539007092198</v>
+        <v>-0.00520833333333337</v>
       </c>
       <c r="S63" s="18" t="n">
-        <v>-0.106660502592929</v>
+        <v>-0.119108744180779</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B64" s="10" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C64" s="10" t="s">
-        <v>156</v>
+        <v>74</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>248</v>
+        <v>212</v>
       </c>
       <c r="E64" s="10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F64" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G64" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H64" s="13" t="n">
-        <v>0.955</v>
+        <v>41.61</v>
       </c>
       <c r="I64" s="13"/>
       <c r="J64" s="13"/>
@@ -5993,14 +5965,14 @@
         <v/>
       </c>
       <c r="M64" s="14" t="n">
-        <v>0.982195121951219</v>
+        <v>43.39175</v>
       </c>
       <c r="N64" s="15" t="str">
         <f aca="false">IF(L64="","",H64/L64-1)</f>
         <v/>
       </c>
       <c r="O64" s="15" t="str">
-        <f aca="false">IF(AND(F64="Accumulate",N64&lt;&gt;"",N64&gt;0),MIN(Policy!$B$4/N64,IF(E64="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F64="Accumulate",N64&lt;&gt;"",N64&gt;0),MIN(Policy!$B$4/(N64+Policy!$B$12),IF(E64="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P64" s="16" t="str">
@@ -6008,13 +5980,13 @@
         <v/>
       </c>
       <c r="Q64" s="17" t="n">
-        <v>-0.0154639175257733</v>
+        <v>-0.0638920134983128</v>
       </c>
       <c r="R64" s="17" t="n">
-        <v>-0.00520833333333337</v>
+        <v>0.0228613569321534</v>
       </c>
       <c r="S64" s="18" t="n">
-        <v>-0.119108744180779</v>
+        <v>-0.136293334939637</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -6031,13 +6003,13 @@
         <v>153</v>
       </c>
       <c r="E65" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F65" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G65" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H65" s="13" t="n">
         <v>1263</v>
@@ -6050,14 +6022,14 @@
         <v/>
       </c>
       <c r="M65" s="14" t="n">
-        <v>1341.8512195122</v>
+        <v>1340.04425</v>
       </c>
       <c r="N65" s="15" t="str">
         <f aca="false">IF(L65="","",H65/L65-1)</f>
         <v/>
       </c>
       <c r="O65" s="15" t="str">
-        <f aca="false">IF(AND(F65="Accumulate",N65&lt;&gt;"",N65&gt;0),MIN(Policy!$B$4/N65,IF(E65="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F65="Accumulate",N65&lt;&gt;"",N65&gt;0),MIN(Policy!$B$4/(N65+Policy!$B$12),IF(E65="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P65" s="16" t="str">
@@ -6085,16 +6057,16 @@
         <v>170</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E66" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F66" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G66" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H66" s="13" t="n">
         <v>80.1</v>
@@ -6107,14 +6079,14 @@
         <v/>
       </c>
       <c r="M66" s="14" t="n">
-        <v>80.8082926829268</v>
+        <v>80.742</v>
       </c>
       <c r="N66" s="15" t="str">
         <f aca="false">IF(L66="","",H66/L66-1)</f>
         <v/>
       </c>
       <c r="O66" s="15" t="str">
-        <f aca="false">IF(AND(F66="Accumulate",N66&lt;&gt;"",N66&gt;0),MIN(Policy!$B$4/N66,IF(E66="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F66="Accumulate",N66&lt;&gt;"",N66&gt;0),MIN(Policy!$B$4/(N66+Policy!$B$12),IF(E66="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P66" s="16" t="str">
@@ -6139,19 +6111,19 @@
         <v>254</v>
       </c>
       <c r="C67" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D67" s="10" t="s">
         <v>255</v>
       </c>
       <c r="E67" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F67" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G67" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H67" s="13" t="n">
         <v>112.85</v>
@@ -6164,14 +6136,14 @@
         <v/>
       </c>
       <c r="M67" s="14" t="n">
-        <v>116.000975609756</v>
+        <v>115.94225</v>
       </c>
       <c r="N67" s="15" t="str">
         <f aca="false">IF(L67="","",H67/L67-1)</f>
         <v/>
       </c>
       <c r="O67" s="15" t="str">
-        <f aca="false">IF(AND(F67="Accumulate",N67&lt;&gt;"",N67&gt;0),MIN(Policy!$B$4/N67,IF(E67="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F67="Accumulate",N67&lt;&gt;"",N67&gt;0),MIN(Policy!$B$4/(N67+Policy!$B$12),IF(E67="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P67" s="16" t="str">
@@ -6199,16 +6171,16 @@
         <v>170</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E68" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F68" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G68" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H68" s="13" t="n">
         <v>24.84</v>
@@ -6221,14 +6193,14 @@
         <v/>
       </c>
       <c r="M68" s="14" t="n">
-        <v>25.7834146341463</v>
+        <v>25.7645</v>
       </c>
       <c r="N68" s="15" t="str">
         <f aca="false">IF(L68="","",H68/L68-1)</f>
         <v/>
       </c>
       <c r="O68" s="15" t="str">
-        <f aca="false">IF(AND(F68="Accumulate",N68&lt;&gt;"",N68&gt;0),MIN(Policy!$B$4/N68,IF(E68="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F68="Accumulate",N68&lt;&gt;"",N68&gt;0),MIN(Policy!$B$4/(N68+Policy!$B$12),IF(E68="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P68" s="16" t="str">
@@ -6259,13 +6231,13 @@
         <v>260</v>
       </c>
       <c r="E69" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F69" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G69" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H69" s="13" t="n">
         <v>52.24</v>
@@ -6278,14 +6250,14 @@
         <v/>
       </c>
       <c r="M69" s="14" t="n">
-        <v>55.6912195121951</v>
+        <v>55.736</v>
       </c>
       <c r="N69" s="15" t="str">
         <f aca="false">IF(L69="","",H69/L69-1)</f>
         <v/>
       </c>
       <c r="O69" s="15" t="str">
-        <f aca="false">IF(AND(F69="Accumulate",N69&lt;&gt;"",N69&gt;0),MIN(Policy!$B$4/N69,IF(E69="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F69="Accumulate",N69&lt;&gt;"",N69&gt;0),MIN(Policy!$B$4/(N69+Policy!$B$12),IF(E69="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P69" s="16" t="str">
@@ -6310,19 +6282,19 @@
         <v>262</v>
       </c>
       <c r="C70" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E70" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F70" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G70" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H70" s="13" t="n">
         <v>141.4</v>
@@ -6335,14 +6307,14 @@
         <v/>
       </c>
       <c r="M70" s="14" t="n">
-        <v>160.669512195122</v>
+        <v>159.7935</v>
       </c>
       <c r="N70" s="15" t="str">
         <f aca="false">IF(L70="","",H70/L70-1)</f>
         <v/>
       </c>
       <c r="O70" s="15" t="str">
-        <f aca="false">IF(AND(F70="Accumulate",N70&lt;&gt;"",N70&gt;0),MIN(Policy!$B$4/N70,IF(E70="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F70="Accumulate",N70&lt;&gt;"",N70&gt;0),MIN(Policy!$B$4/(N70+Policy!$B$12),IF(E70="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P70" s="16" t="str">
@@ -6373,13 +6345,13 @@
         <v>265</v>
       </c>
       <c r="E71" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F71" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G71" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H71" s="13" t="n">
         <v>107</v>
@@ -6392,14 +6364,14 @@
         <v/>
       </c>
       <c r="M71" s="14" t="n">
-        <v>125.956097560976</v>
+        <v>125.38</v>
       </c>
       <c r="N71" s="15" t="str">
         <f aca="false">IF(L71="","",H71/L71-1)</f>
         <v/>
       </c>
       <c r="O71" s="15" t="str">
-        <f aca="false">IF(AND(F71="Accumulate",N71&lt;&gt;"",N71&gt;0),MIN(Policy!$B$4/N71,IF(E71="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F71="Accumulate",N71&lt;&gt;"",N71&gt;0),MIN(Policy!$B$4/(N71+Policy!$B$12),IF(E71="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P71" s="16" t="str">
@@ -6430,13 +6402,13 @@
         <v>209</v>
       </c>
       <c r="E72" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F72" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G72" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H72" s="13" t="n">
         <v>377.8</v>
@@ -6449,14 +6421,14 @@
         <v/>
       </c>
       <c r="M72" s="14" t="n">
-        <v>403.287804878049</v>
+        <v>402.975</v>
       </c>
       <c r="N72" s="15" t="str">
         <f aca="false">IF(L72="","",H72/L72-1)</f>
         <v/>
       </c>
       <c r="O72" s="15" t="str">
-        <f aca="false">IF(AND(F72="Accumulate",N72&lt;&gt;"",N72&gt;0),MIN(Policy!$B$4/N72,IF(E72="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F72="Accumulate",N72&lt;&gt;"",N72&gt;0),MIN(Policy!$B$4/(N72+Policy!$B$12),IF(E72="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P72" s="16" t="str">
@@ -6487,13 +6459,13 @@
         <v>265</v>
       </c>
       <c r="E73" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F73" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G73" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H73" s="13" t="n">
         <v>71.5</v>
@@ -6506,14 +6478,14 @@
         <v/>
       </c>
       <c r="M73" s="14" t="n">
-        <v>82.5653658536585</v>
+        <v>82.0145</v>
       </c>
       <c r="N73" s="15" t="str">
         <f aca="false">IF(L73="","",H73/L73-1)</f>
         <v/>
       </c>
       <c r="O73" s="15" t="str">
-        <f aca="false">IF(AND(F73="Accumulate",N73&lt;&gt;"",N73&gt;0),MIN(Policy!$B$4/N73,IF(E73="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F73="Accumulate",N73&lt;&gt;"",N73&gt;0),MIN(Policy!$B$4/(N73+Policy!$B$12),IF(E73="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P73" s="16" t="str">
@@ -6544,13 +6516,13 @@
         <v>272</v>
       </c>
       <c r="E74" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F74" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G74" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H74" s="13" t="n">
         <v>2.24</v>
@@ -6563,14 +6535,14 @@
         <v/>
       </c>
       <c r="M74" s="14" t="n">
-        <v>2.36682926829268</v>
+        <v>2.3665</v>
       </c>
       <c r="N74" s="15" t="str">
         <f aca="false">IF(L74="","",H74/L74-1)</f>
         <v/>
       </c>
       <c r="O74" s="15" t="str">
-        <f aca="false">IF(AND(F74="Accumulate",N74&lt;&gt;"",N74&gt;0),MIN(Policy!$B$4/N74,IF(E74="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F74="Accumulate",N74&lt;&gt;"",N74&gt;0),MIN(Policy!$B$4/(N74+Policy!$B$12),IF(E74="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P74" s="16" t="str">
@@ -6595,19 +6567,19 @@
         <v>274</v>
       </c>
       <c r="C75" s="10" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D75" s="10" t="s">
         <v>143</v>
       </c>
       <c r="E75" s="10" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F75" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G75" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H75" s="13" t="n">
         <v>41.41</v>
@@ -6620,14 +6592,14 @@
         <v/>
       </c>
       <c r="M75" s="14" t="n">
-        <v>44.4109756097561</v>
+        <v>44.44175</v>
       </c>
       <c r="N75" s="15" t="str">
         <f aca="false">IF(L75="","",H75/L75-1)</f>
         <v/>
       </c>
       <c r="O75" s="15" t="str">
-        <f aca="false">IF(AND(F75="Accumulate",N75&lt;&gt;"",N75&gt;0),MIN(Policy!$B$4/N75,IF(E75="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F75="Accumulate",N75&lt;&gt;"",N75&gt;0),MIN(Policy!$B$4/(N75+Policy!$B$12),IF(E75="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P75" s="16" t="str">
@@ -6658,13 +6630,13 @@
         <v>277</v>
       </c>
       <c r="E76" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F76" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G76" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H76" s="13" t="n">
         <v>297.75</v>
@@ -6677,14 +6649,14 @@
         <v/>
       </c>
       <c r="M76" s="14" t="n">
-        <v>378.423170731707</v>
+        <v>378.495</v>
       </c>
       <c r="N76" s="15" t="str">
         <f aca="false">IF(L76="","",H76/L76-1)</f>
         <v/>
       </c>
       <c r="O76" s="15" t="str">
-        <f aca="false">IF(AND(F76="Accumulate",N76&lt;&gt;"",N76&gt;0),MIN(Policy!$B$4/N76,IF(E76="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F76="Accumulate",N76&lt;&gt;"",N76&gt;0),MIN(Policy!$B$4/(N76+Policy!$B$12),IF(E76="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P76" s="16" t="str">
@@ -6715,13 +6687,13 @@
         <v>280</v>
       </c>
       <c r="E77" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F77" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G77" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H77" s="13" t="n">
         <v>75.6</v>
@@ -6734,14 +6706,14 @@
         <v/>
       </c>
       <c r="M77" s="14" t="n">
-        <v>92.3009756097561</v>
+        <v>92.1395</v>
       </c>
       <c r="N77" s="15" t="str">
         <f aca="false">IF(L77="","",H77/L77-1)</f>
         <v/>
       </c>
       <c r="O77" s="15" t="str">
-        <f aca="false">IF(AND(F77="Accumulate",N77&lt;&gt;"",N77&gt;0),MIN(Policy!$B$4/N77,IF(E77="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F77="Accumulate",N77&lt;&gt;"",N77&gt;0),MIN(Policy!$B$4/(N77+Policy!$B$12),IF(E77="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P77" s="16" t="str">
@@ -6772,13 +6744,13 @@
         <v>283</v>
       </c>
       <c r="E78" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F78" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G78" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H78" s="13" t="n">
         <v>2.13</v>
@@ -6791,14 +6763,14 @@
         <v/>
       </c>
       <c r="M78" s="14" t="n">
-        <v>2.24878048780488</v>
+        <v>2.249</v>
       </c>
       <c r="N78" s="15" t="str">
         <f aca="false">IF(L78="","",H78/L78-1)</f>
         <v/>
       </c>
       <c r="O78" s="15" t="str">
-        <f aca="false">IF(AND(F78="Accumulate",N78&lt;&gt;"",N78&gt;0),MIN(Policy!$B$4/N78,IF(E78="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F78="Accumulate",N78&lt;&gt;"",N78&gt;0),MIN(Policy!$B$4/(N78+Policy!$B$12),IF(E78="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P78" s="16" t="str">
@@ -6826,16 +6798,16 @@
         <v>170</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="E79" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F79" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H79" s="13" t="n">
         <v>424.8</v>
@@ -6848,14 +6820,14 @@
         <v/>
       </c>
       <c r="M79" s="14" t="n">
-        <v>486.307317073171</v>
+        <v>482.89</v>
       </c>
       <c r="N79" s="15" t="str">
         <f aca="false">IF(L79="","",H79/L79-1)</f>
         <v/>
       </c>
       <c r="O79" s="15" t="str">
-        <f aca="false">IF(AND(F79="Accumulate",N79&lt;&gt;"",N79&gt;0),MIN(Policy!$B$4/N79,IF(E79="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F79="Accumulate",N79&lt;&gt;"",N79&gt;0),MIN(Policy!$B$4/(N79+Policy!$B$12),IF(E79="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P79" s="16" t="str">
@@ -6886,13 +6858,13 @@
         <v>288</v>
       </c>
       <c r="E80" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F80" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G80" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H80" s="13" t="n">
         <v>1.08</v>
@@ -6905,14 +6877,14 @@
         <v/>
       </c>
       <c r="M80" s="14" t="n">
-        <v>1.21609756097561</v>
+        <v>1.2135</v>
       </c>
       <c r="N80" s="15" t="str">
         <f aca="false">IF(L80="","",H80/L80-1)</f>
         <v/>
       </c>
       <c r="O80" s="15" t="str">
-        <f aca="false">IF(AND(F80="Accumulate",N80&lt;&gt;"",N80&gt;0),MIN(Policy!$B$4/N80,IF(E80="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F80="Accumulate",N80&lt;&gt;"",N80&gt;0),MIN(Policy!$B$4/(N80+Policy!$B$12),IF(E80="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P80" s="16" t="str">
@@ -6943,13 +6915,13 @@
         <v>291</v>
       </c>
       <c r="E81" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F81" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G81" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H81" s="13" t="n">
         <v>1.83</v>
@@ -6962,14 +6934,14 @@
         <v/>
       </c>
       <c r="M81" s="14" t="n">
-        <v>1.96878048780488</v>
+        <v>1.96625</v>
       </c>
       <c r="N81" s="15" t="str">
         <f aca="false">IF(L81="","",H81/L81-1)</f>
         <v/>
       </c>
       <c r="O81" s="15" t="str">
-        <f aca="false">IF(AND(F81="Accumulate",N81&lt;&gt;"",N81&gt;0),MIN(Policy!$B$4/N81,IF(E81="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F81="Accumulate",N81&lt;&gt;"",N81&gt;0),MIN(Policy!$B$4/(N81+Policy!$B$12),IF(E81="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P81" s="16" t="str">
@@ -7000,13 +6972,13 @@
         <v>294</v>
       </c>
       <c r="E82" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F82" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G82" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H82" s="13" t="n">
         <v>2.07</v>
@@ -7019,14 +6991,14 @@
         <v/>
       </c>
       <c r="M82" s="14" t="n">
-        <v>2.22829268292683</v>
+        <v>2.226</v>
       </c>
       <c r="N82" s="15" t="str">
         <f aca="false">IF(L82="","",H82/L82-1)</f>
         <v/>
       </c>
       <c r="O82" s="15" t="str">
-        <f aca="false">IF(AND(F82="Accumulate",N82&lt;&gt;"",N82&gt;0),MIN(Policy!$B$4/N82,IF(E82="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F82="Accumulate",N82&lt;&gt;"",N82&gt;0),MIN(Policy!$B$4/(N82+Policy!$B$12),IF(E82="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P82" s="16" t="str">
@@ -7057,13 +7029,13 @@
         <v>272</v>
       </c>
       <c r="E83" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F83" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G83" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H83" s="13" t="n">
         <v>1.19</v>
@@ -7076,14 +7048,14 @@
         <v/>
       </c>
       <c r="M83" s="14" t="n">
-        <v>1.32707317073171</v>
+        <v>1.3235</v>
       </c>
       <c r="N83" s="15" t="str">
         <f aca="false">IF(L83="","",H83/L83-1)</f>
         <v/>
       </c>
       <c r="O83" s="15" t="str">
-        <f aca="false">IF(AND(F83="Accumulate",N83&lt;&gt;"",N83&gt;0),MIN(Policy!$B$4/N83,IF(E83="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F83="Accumulate",N83&lt;&gt;"",N83&gt;0),MIN(Policy!$B$4/(N83+Policy!$B$12),IF(E83="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P83" s="16" t="str">
@@ -7114,13 +7086,13 @@
         <v>291</v>
       </c>
       <c r="E84" s="10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F84" s="21" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G84" s="12" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H84" s="13" t="n">
         <v>2.19</v>
@@ -7133,14 +7105,14 @@
         <v/>
       </c>
       <c r="M84" s="14" t="n">
-        <v>2.54146341463415</v>
+        <v>2.53425</v>
       </c>
       <c r="N84" s="15" t="str">
         <f aca="false">IF(L84="","",H84/L84-1)</f>
         <v/>
       </c>
       <c r="O84" s="15" t="str">
-        <f aca="false">IF(AND(F84="Accumulate",N84&lt;&gt;"",N84&gt;0),MIN(Policy!$B$4/N84,IF(E84="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
+        <f aca="false">IF(AND(F84="Accumulate",N84&lt;&gt;"",N84&gt;0),MIN(Policy!$B$4/(N84+Policy!$B$12),IF(E84="Stock",Policy!$B$5,Policy!$B$6)),"")</f>
         <v/>
       </c>
       <c r="P84" s="16" t="str">
@@ -7166,11 +7138,11 @@
       </c>
       <c r="O86" s="22" t="n">
         <f aca="false">SUM(O2:O84)</f>
-        <v>0.404605758411774</v>
+        <v>0.372698624375118</v>
       </c>
       <c r="P86" s="23" t="n">
         <f aca="false">SUM(P2:P84)</f>
-        <v>404605.758411774</v>
+        <v>372698.624375118</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7214,10 +7186,10 @@
   <sheetData>
     <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C1" s="5" t="s">
         <v>302</v>
@@ -7294,7 +7266,7 @@
         <v>-0.144859813084112</v>
       </c>
       <c r="L2" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M2" s="29" t="s">
         <v>313</v>
@@ -7341,7 +7313,7 @@
         <v>-0.22887323943662</v>
       </c>
       <c r="L3" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M3" s="29" t="s">
         <v>314</v>
@@ -7388,7 +7360,7 @@
         <v>-0.142857142857143</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M4" s="29" t="s">
         <v>315</v>
@@ -7435,7 +7407,7 @@
         <v>-0.179310344827586</v>
       </c>
       <c r="L5" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M5" s="29" t="s">
         <v>316</v>
@@ -7482,7 +7454,7 @@
         <v>-0.108786610878661</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="M6" s="29" t="s">
         <v>317</v>
@@ -7529,7 +7501,7 @@
         <v>-0.130252100840336</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="M7" s="29" t="s">
         <v>318</v>
@@ -7537,10 +7509,10 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C8" s="24" t="n">
         <v>0.955</v>
@@ -7576,7 +7548,7 @@
         <v>-0.00520833333333337</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="M8" s="29" t="s">
         <v>319</v>
@@ -7623,7 +7595,7 @@
         <v>-0.0427350427350426</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="M9" s="29" t="s">
         <v>320</v>
@@ -7631,10 +7603,10 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="4" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="C10" s="24" t="n">
         <v>4.24</v>
@@ -7670,7 +7642,7 @@
         <v>-0.00469483568075102</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="M10" s="29" t="s">
         <v>321</v>
@@ -7717,7 +7689,7 @@
         <v>0.36230269266481</v>
       </c>
       <c r="L11" s="9" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="M11" s="29" t="s">
         <v>322</v>
@@ -7725,10 +7697,10 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="4" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="C12" s="24" t="n">
         <v>3.98</v>
@@ -7764,7 +7736,7 @@
         <v>-0.038647342995169</v>
       </c>
       <c r="L12" s="9" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="M12" s="29" t="s">
         <v>323</v>
@@ -7811,7 +7783,7 @@
         <v>0.13105009906595</v>
       </c>
       <c r="L13" s="9" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="M13" s="29" t="s">
         <v>324</v>
@@ -7858,7 +7830,7 @@
         <v>0.718009478672986</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="M14" s="29" t="s">
         <v>325</v>
@@ -7905,7 +7877,7 @@
         <v>0.218713450292398</v>
       </c>
       <c r="L15" s="9" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="M15" s="29" t="s">
         <v>326</v>
@@ -8097,7 +8069,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q23"/>
+  <dimension ref="A1:Q12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10"/>
@@ -8172,7 +8144,7 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>367</v>
@@ -8231,7 +8203,7 @@
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="4" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>370</v>
@@ -8290,7 +8262,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>367</v>
@@ -8349,7 +8321,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>367</v>
@@ -8465,672 +8437,39 @@
         <v>3.275</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="C7" s="4" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="9" t="s">
         <v>375</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="E7" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="F7" s="31" t="n">
-        <v>229.33</v>
-      </c>
-      <c r="G7" s="32" t="n">
-        <v>7.825</v>
-      </c>
-      <c r="H7" s="23" t="n">
-        <f aca="false">G7*100</f>
-        <v>782.5</v>
-      </c>
-      <c r="I7" s="31" t="n">
-        <v>237.825</v>
-      </c>
-      <c r="J7" s="33" t="n">
-        <f aca="false">I7/F7-1</f>
-        <v>0.0370426895739762</v>
-      </c>
-      <c r="K7" s="32" t="n">
-        <v>12.175</v>
-      </c>
-      <c r="L7" s="34" t="n">
-        <f aca="false">IF(K7="","open",K7/G7)</f>
-        <v>1.55591054313099</v>
-      </c>
-      <c r="M7" s="7" t="n">
-        <v>0.394779768673195</v>
-      </c>
-      <c r="N7" s="7" t="n">
-        <v>0.340953465060969</v>
-      </c>
-      <c r="O7" s="35" t="n">
-        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H7)</f>
-        <v>12</v>
-      </c>
-      <c r="P7" s="23" t="n">
-        <f aca="false">O7*H7</f>
-        <v>9390</v>
-      </c>
-      <c r="Q7" s="36" t="n">
-        <f aca="false">G7*(1-0.5)</f>
-        <v>3.9125</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="O8" s="9" t="s">
         <v>376</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="E8" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="F8" s="31" t="n">
-        <v>751.38</v>
-      </c>
-      <c r="G8" s="32" t="n">
-        <v>25.26</v>
-      </c>
-      <c r="H8" s="23" t="n">
-        <f aca="false">G8*100</f>
-        <v>2526</v>
-      </c>
-      <c r="I8" s="31" t="n">
-        <v>776.26</v>
-      </c>
-      <c r="J8" s="33" t="n">
-        <f aca="false">I8/F8-1</f>
-        <v>0.0331124065053634</v>
-      </c>
-      <c r="K8" s="32" t="n">
-        <v>48.74</v>
-      </c>
-      <c r="L8" s="34" t="n">
-        <f aca="false">IF(K8="","open",K8/G8)</f>
-        <v>1.92953285827395</v>
-      </c>
-      <c r="M8" s="7" t="n">
-        <v>0.368962735908992</v>
-      </c>
-      <c r="N8" s="7" t="n">
-        <v>0.194792627653838</v>
-      </c>
-      <c r="O8" s="35" t="n">
-        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H8)</f>
-        <v>3</v>
-      </c>
       <c r="P8" s="23" t="n">
-        <f aca="false">O8*H8</f>
-        <v>7578</v>
-      </c>
-      <c r="Q8" s="36" t="n">
-        <f aca="false">G8*(1-0.5)</f>
-        <v>12.63</v>
+        <f aca="false">SUM(P2:P6)</f>
+        <v>47466.5</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>367</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="O9" s="9" t="s">
         <v>377</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="E9" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="F9" s="31" t="n">
-        <v>778.57</v>
-      </c>
-      <c r="G9" s="32" t="n">
-        <v>20.395</v>
-      </c>
-      <c r="H9" s="23" t="n">
-        <f aca="false">G9*100</f>
-        <v>2039.5</v>
-      </c>
-      <c r="I9" s="31" t="n">
-        <v>799.395</v>
-      </c>
-      <c r="J9" s="33" t="n">
-        <f aca="false">I9/F9-1</f>
-        <v>0.0267477555004687</v>
-      </c>
-      <c r="K9" s="32" t="n">
-        <v>55.605</v>
-      </c>
-      <c r="L9" s="34" t="n">
-        <f aca="false">IF(K9="","open",K9/G9)</f>
-        <v>2.72640353027703</v>
-      </c>
-      <c r="M9" s="7" t="n">
-        <v>0.363472788907844</v>
-      </c>
-      <c r="N9" s="7" t="n">
-        <v>0.133650255019125</v>
-      </c>
-      <c r="O9" s="35" t="n">
-        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H9)</f>
-        <v>4</v>
-      </c>
       <c r="P9" s="23" t="n">
-        <f aca="false">O9*H9</f>
-        <v>8158</v>
-      </c>
-      <c r="Q9" s="36" t="n">
-        <f aca="false">G9*(1-0.5)</f>
-        <v>10.1975</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="C10" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="E10" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="F10" s="31" t="n">
-        <v>141.55</v>
-      </c>
-      <c r="G10" s="32" t="n">
-        <v>10.15</v>
-      </c>
-      <c r="H10" s="23" t="n">
-        <f aca="false">G10*100</f>
-        <v>1015</v>
-      </c>
-      <c r="I10" s="31" t="n">
-        <v>124.85</v>
-      </c>
-      <c r="J10" s="33" t="n">
-        <f aca="false">I10/F10-1</f>
-        <v>-0.117979512539739</v>
-      </c>
-      <c r="K10" s="32"/>
-      <c r="L10" s="34" t="str">
-        <f aca="false">IF(K10="","open",K10/G10)</f>
-        <v>open</v>
-      </c>
-      <c r="M10" s="7" t="n">
-        <v>0.339881226108832</v>
-      </c>
-      <c r="N10" s="7" t="n">
-        <v>0.566607287616487</v>
-      </c>
-      <c r="O10" s="35" t="n">
-        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H10)</f>
-        <v>9</v>
-      </c>
-      <c r="P10" s="23" t="n">
-        <f aca="false">O10*H10</f>
-        <v>9135</v>
-      </c>
-      <c r="Q10" s="36" t="n">
-        <f aca="false">G10*(1-0.5)</f>
-        <v>5.075</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="E11" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="F11" s="31" t="n">
-        <v>168.79</v>
-      </c>
-      <c r="G11" s="32" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="H11" s="23" t="n">
-        <f aca="false">G11*100</f>
-        <v>565</v>
-      </c>
-      <c r="I11" s="31" t="n">
-        <v>180.65</v>
-      </c>
-      <c r="J11" s="33" t="n">
-        <f aca="false">I11/F11-1</f>
-        <v>0.0702648261152912</v>
-      </c>
-      <c r="K11" s="32"/>
-      <c r="L11" s="34" t="str">
-        <f aca="false">IF(K11="","open",K11/G11)</f>
-        <v>open</v>
-      </c>
-      <c r="M11" s="7" t="n">
-        <v>0.289317614247436</v>
-      </c>
-      <c r="N11" s="7" t="n">
-        <v>0.278166458712079</v>
-      </c>
-      <c r="O11" s="35" t="n">
-        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H11)</f>
-        <v>17</v>
-      </c>
-      <c r="P11" s="23" t="n">
-        <f aca="false">O11*H11</f>
-        <v>9605</v>
-      </c>
-      <c r="Q11" s="36" t="n">
-        <f aca="false">G11*(1-0.5)</f>
-        <v>2.825</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="E12" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="F12" s="31" t="n">
-        <v>229.33</v>
-      </c>
-      <c r="G12" s="32" t="n">
-        <v>9.725</v>
-      </c>
-      <c r="H12" s="23" t="n">
-        <f aca="false">G12*100</f>
-        <v>972.5</v>
-      </c>
-      <c r="I12" s="31" t="n">
-        <v>249.725</v>
-      </c>
-      <c r="J12" s="33" t="n">
-        <f aca="false">I12/F12-1</f>
-        <v>0.0889329786770157</v>
-      </c>
-      <c r="K12" s="32"/>
-      <c r="L12" s="34" t="str">
-        <f aca="false">IF(K12="","open",K12/G12)</f>
-        <v>open</v>
-      </c>
-      <c r="M12" s="7" t="n">
-        <v>0.273762735822154</v>
-      </c>
-      <c r="N12" s="7" t="n">
-        <v>0.335245429054431</v>
-      </c>
-      <c r="O12" s="35" t="n">
-        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H12)</f>
-        <v>10</v>
-      </c>
-      <c r="P12" s="23" t="n">
-        <f aca="false">O12*H12</f>
-        <v>9725</v>
-      </c>
-      <c r="Q12" s="36" t="n">
-        <f aca="false">G12*(1-0.5)</f>
-        <v>4.8625</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="E13" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="F13" s="31" t="n">
-        <v>351.6</v>
-      </c>
-      <c r="G13" s="32" t="n">
-        <v>13.675</v>
-      </c>
-      <c r="H13" s="23" t="n">
-        <f aca="false">G13*100</f>
-        <v>1367.5</v>
-      </c>
-      <c r="I13" s="31" t="n">
-        <v>383.675</v>
-      </c>
-      <c r="J13" s="33" t="n">
-        <f aca="false">I13/F13-1</f>
-        <v>0.0912258248009101</v>
-      </c>
-      <c r="K13" s="32"/>
-      <c r="L13" s="34" t="str">
-        <f aca="false">IF(K13="","open",K13/G13)</f>
-        <v>open</v>
-      </c>
-      <c r="M13" s="7" t="n">
-        <v>0.263871389642364</v>
-      </c>
-      <c r="N13" s="7" t="n">
-        <v>0.324467860851498</v>
-      </c>
-      <c r="O13" s="35" t="n">
-        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H13)</f>
-        <v>7</v>
-      </c>
-      <c r="P13" s="23" t="n">
-        <f aca="false">O13*H13</f>
-        <v>9572.5</v>
-      </c>
-      <c r="Q13" s="36" t="n">
-        <f aca="false">G13*(1-0.5)</f>
-        <v>6.8375</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="E14" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="F14" s="31" t="n">
-        <v>384.5</v>
-      </c>
-      <c r="G14" s="32" t="n">
-        <v>5.525</v>
-      </c>
-      <c r="H14" s="23" t="n">
-        <f aca="false">G14*100</f>
-        <v>552.5</v>
-      </c>
-      <c r="I14" s="31" t="n">
-        <v>359.475</v>
-      </c>
-      <c r="J14" s="33" t="n">
-        <f aca="false">I14/F14-1</f>
-        <v>-0.0650845253576072</v>
-      </c>
-      <c r="K14" s="32"/>
-      <c r="L14" s="34" t="str">
-        <f aca="false">IF(K14="","open",K14/G14)</f>
-        <v>open</v>
-      </c>
-      <c r="M14" s="7" t="n">
-        <v>0.22652457613958</v>
-      </c>
-      <c r="N14" s="7" t="n">
-        <v>0.214702125013975</v>
-      </c>
-      <c r="O14" s="35" t="n">
-        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H14)</f>
-        <v>18</v>
-      </c>
-      <c r="P14" s="23" t="n">
-        <f aca="false">O14*H14</f>
-        <v>9945</v>
-      </c>
-      <c r="Q14" s="36" t="n">
-        <f aca="false">G14*(1-0.5)</f>
-        <v>2.7625</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="E15" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="F15" s="31" t="n">
-        <v>336.08</v>
-      </c>
-      <c r="G15" s="32" t="n">
-        <v>7.75</v>
-      </c>
-      <c r="H15" s="23" t="n">
-        <f aca="false">G15*100</f>
-        <v>775</v>
-      </c>
-      <c r="I15" s="31" t="n">
-        <v>362.75</v>
-      </c>
-      <c r="J15" s="33" t="n">
-        <f aca="false">I15/F15-1</f>
-        <v>0.0793561056891217</v>
-      </c>
-      <c r="K15" s="32"/>
-      <c r="L15" s="34" t="str">
-        <f aca="false">IF(K15="","open",K15/G15)</f>
-        <v>open</v>
-      </c>
-      <c r="M15" s="7" t="n">
-        <v>0.237030626911625</v>
-      </c>
-      <c r="N15" s="7" t="n">
-        <v>0.236173523215233</v>
-      </c>
-      <c r="O15" s="35" t="n">
-        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H15)</f>
-        <v>12</v>
-      </c>
-      <c r="P15" s="23" t="n">
-        <f aca="false">O15*H15</f>
-        <v>9300</v>
-      </c>
-      <c r="Q15" s="36" t="n">
-        <f aca="false">G15*(1-0.5)</f>
-        <v>3.875</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="E16" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="F16" s="31" t="n">
-        <v>751.38</v>
-      </c>
-      <c r="G16" s="32" t="n">
-        <v>11.02</v>
-      </c>
-      <c r="H16" s="23" t="n">
-        <f aca="false">G16*100</f>
-        <v>1102</v>
-      </c>
-      <c r="I16" s="31" t="n">
-        <v>800.02</v>
-      </c>
-      <c r="J16" s="33" t="n">
-        <f aca="false">I16/F16-1</f>
-        <v>0.0647342223641831</v>
-      </c>
-      <c r="K16" s="32"/>
-      <c r="L16" s="34" t="str">
-        <f aca="false">IF(K16="","open",K16/G16)</f>
-        <v>open</v>
-      </c>
-      <c r="M16" s="7" t="n">
-        <v>0.224316324820298</v>
-      </c>
-      <c r="N16" s="7" t="n">
-        <v>0.174740994153321</v>
-      </c>
-      <c r="O16" s="35" t="n">
-        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H16)</f>
-        <v>9</v>
-      </c>
-      <c r="P16" s="23" t="n">
-        <f aca="false">O16*H16</f>
-        <v>9918</v>
-      </c>
-      <c r="Q16" s="36" t="n">
-        <f aca="false">G16*(1-0.5)</f>
-        <v>5.51</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>380</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>369</v>
-      </c>
-      <c r="E17" s="30" t="n">
-        <v>70</v>
-      </c>
-      <c r="F17" s="31" t="n">
-        <v>778.57</v>
-      </c>
-      <c r="G17" s="32" t="n">
-        <v>4.66</v>
-      </c>
-      <c r="H17" s="23" t="n">
-        <f aca="false">G17*100</f>
-        <v>466</v>
-      </c>
-      <c r="I17" s="31" t="n">
-        <v>821.66</v>
-      </c>
-      <c r="J17" s="33" t="n">
-        <f aca="false">I17/F17-1</f>
-        <v>0.0553450556790012</v>
-      </c>
-      <c r="K17" s="32"/>
-      <c r="L17" s="34" t="str">
-        <f aca="false">IF(K17="","open",K17/G17)</f>
-        <v>open</v>
-      </c>
-      <c r="M17" s="7" t="n">
-        <v>0.171791316837144</v>
-      </c>
-      <c r="N17" s="7" t="n">
-        <v>0.114405791873116</v>
-      </c>
-      <c r="O17" s="35" t="n">
-        <f aca="false">INT(Policy!$B$2*Policy!$B$11/H17)</f>
-        <v>21</v>
-      </c>
-      <c r="P17" s="23" t="n">
-        <f aca="false">O17*H17</f>
-        <v>9786</v>
-      </c>
-      <c r="Q17" s="36" t="n">
-        <f aca="false">G17*(1-0.5)</f>
-        <v>2.33</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="9" t="s">
-        <v>388</v>
-      </c>
-      <c r="O19" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="P19" s="23" t="n">
-        <f aca="false">SUM(P2:P17)</f>
-        <v>149579</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O20" s="9" t="s">
-        <v>390</v>
-      </c>
-      <c r="P20" s="23" t="n">
         <f aca="false">Policy!$B$2*Policy!$B$10</f>
         <v>50000</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O21" s="9" t="s">
-        <v>391</v>
-      </c>
-      <c r="P21" s="0" t="str">
-        <f aca="false">IF(P19&lt;=P20,"Yes","No: pick fewer trades")</f>
-        <v>No: pick fewer trades</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="2" t="s">
-        <v>392</v>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="O10" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="P10" s="0" t="str">
+        <f aca="false">IF(P8&lt;=P9,"Yes","No: pick fewer trades")</f>
+        <v>Yes</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>379</v>
       </c>
     </row>
   </sheetData>
@@ -9165,48 +8504,48 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="5" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="37" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="B2" s="37" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C2" s="37" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D2" s="37" t="n">
         <v>65.08</v>
@@ -9218,16 +8557,16 @@
         <v>55.59</v>
       </c>
       <c r="G2" s="37" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="H2" s="37" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="I2" s="37" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="J2" s="37" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="K2" s="37"/>
     </row>
